--- a/worlds/spyro_aht/setup/Gem Research.xlsx
+++ b/worlds/spyro_aht/setup/Gem Research.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean\Downloads\Archipelago Stuff\.apworlds\PhoenixAP\worlds\spyro_aht\setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9AB485-0CCD-4728-BBB3-575D6C6EF4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F048B4-AD8A-4576-9111-2EFA38737D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="697" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="697" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dragon Kingdom CONDENSING" sheetId="10" r:id="rId1"/>
@@ -1662,30 +1662,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{97E416E5-8FB3-43B0-B976-8A1F74DE1D92}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Sean Stanley:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-can DJ it and then use E since E is needed to get into here</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -2975,7 +2951,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3125" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3125" uniqueCount="578">
   <si>
     <t>Description</t>
   </si>
@@ -4700,6 +4676,15 @@
   </si>
   <si>
     <t>NON-BLINK TOTAL</t>
+  </si>
+  <si>
+    <t>E + DJ</t>
+  </si>
+  <si>
+    <t>E + DJ + W</t>
+  </si>
+  <si>
+    <t>Immediates under dark gem + eskimole under snowman</t>
   </si>
 </sst>
 </file>
@@ -5231,43 +5216,13 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5297,13 +5252,31 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5318,7 +5291,31 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5330,46 +5327,34 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -5678,44 +5663,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="151" t="str">
+      <c r="A1" s="118" t="str">
         <f>"Dragon Kingdom (total " &amp; F23 &amp; ")"</f>
         <v>Dragon Kingdom (total 22722)</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="152"/>
-      <c r="H1" s="152"/>
-      <c r="I1" s="152"/>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="153"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="120"/>
       <c r="N1" s="2"/>
       <c r="P1" s="2"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="121" t="s">
         <v>375</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="134" t="s">
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124" t="s">
         <v>392</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="137" t="s">
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="127" t="s">
         <v>376</v>
       </c>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="139"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="129"/>
     </row>
     <row r="3" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="s">
@@ -5756,24 +5741,24 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A4" s="140" t="s">
+      <c r="A4" s="136" t="s">
         <v>435</v>
       </c>
-      <c r="B4" s="154"/>
-      <c r="C4" s="154"/>
-      <c r="D4" s="155"/>
-      <c r="E4" s="148" t="s">
+      <c r="B4" s="137"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="152" t="s">
         <v>433</v>
       </c>
-      <c r="F4" s="149"/>
-      <c r="G4" s="149"/>
-      <c r="H4" s="150"/>
-      <c r="I4" s="122" t="s">
+      <c r="F4" s="153"/>
+      <c r="G4" s="153"/>
+      <c r="H4" s="154"/>
+      <c r="I4" s="150" t="s">
         <v>439</v>
       </c>
-      <c r="J4" s="123"/>
-      <c r="K4" s="123"/>
-      <c r="L4" s="124"/>
+      <c r="J4" s="151"/>
+      <c r="K4" s="151"/>
+      <c r="L4" s="155"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5" s="10" t="s">
@@ -6005,12 +5990,12 @@
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A11" s="118" t="s">
+      <c r="A11" s="133" t="s">
         <v>436</v>
       </c>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="120"/>
+      <c r="B11" s="134"/>
+      <c r="C11" s="134"/>
+      <c r="D11" s="135"/>
       <c r="E11" s="16" t="s">
         <v>65</v>
       </c>
@@ -6132,12 +6117,12 @@
         <v>7685</v>
       </c>
       <c r="H14" s="18"/>
-      <c r="I14" s="122" t="s">
+      <c r="I14" s="150" t="s">
         <v>440</v>
       </c>
-      <c r="J14" s="123"/>
-      <c r="K14" s="123"/>
-      <c r="L14" s="124"/>
+      <c r="J14" s="151"/>
+      <c r="K14" s="151"/>
+      <c r="L14" s="155"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A15" s="10" t="s">
@@ -6152,12 +6137,12 @@
       <c r="D15" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="E15" s="148" t="s">
+      <c r="E15" s="152" t="s">
         <v>434</v>
       </c>
-      <c r="F15" s="149"/>
-      <c r="G15" s="149"/>
-      <c r="H15" s="150"/>
+      <c r="F15" s="153"/>
+      <c r="G15" s="153"/>
+      <c r="H15" s="154"/>
       <c r="I15" s="22" t="s">
         <v>85</v>
       </c>
@@ -6248,12 +6233,12 @@
       </c>
     </row>
     <row r="18" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="118" t="s">
+      <c r="A18" s="133" t="s">
         <v>437</v>
       </c>
-      <c r="B18" s="119"/>
-      <c r="C18" s="119"/>
-      <c r="D18" s="120"/>
+      <c r="B18" s="134"/>
+      <c r="C18" s="134"/>
+      <c r="D18" s="135"/>
       <c r="E18" s="16" t="s">
         <v>265</v>
       </c>
@@ -6430,12 +6415,12 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A25" s="118" t="s">
+      <c r="A25" s="133" t="s">
         <v>438</v>
       </c>
-      <c r="B25" s="119"/>
-      <c r="C25" s="119"/>
-      <c r="D25" s="120"/>
+      <c r="B25" s="134"/>
+      <c r="C25" s="134"/>
+      <c r="D25" s="135"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A26" s="10" t="s">
@@ -6511,6 +6496,11 @@
     <sortCondition ref="L15:L18"/>
   </sortState>
   <mergeCells count="12">
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A25:D25"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:H2"/>
@@ -6518,11 +6508,6 @@
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="E4:H4"/>
     <mergeCell ref="I4:L4"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A25:D25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -6551,44 +6536,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="128" t="str">
+      <c r="A1" s="156" t="str">
         <f>"Lost Cities (total " &amp; F32 &amp; ")"</f>
         <v>Lost Cities (total 34247)</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="129"/>
-      <c r="J1" s="129"/>
-      <c r="K1" s="129"/>
-      <c r="L1" s="130"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="157"/>
+      <c r="J1" s="157"/>
+      <c r="K1" s="157"/>
+      <c r="L1" s="158"/>
       <c r="N1" s="2"/>
       <c r="P1" s="2"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="121" t="s">
         <v>98</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="134" t="s">
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124" t="s">
         <v>146</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="137" t="s">
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="127" t="s">
         <v>170</v>
       </c>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="139"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="129"/>
     </row>
     <row r="3" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="36" t="s">
@@ -6629,24 +6614,24 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A4" s="118" t="s">
+      <c r="A4" s="133" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="120"/>
-      <c r="E4" s="143" t="s">
+      <c r="B4" s="134"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="139" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144"/>
-      <c r="I4" s="145" t="s">
+      <c r="F4" s="140"/>
+      <c r="G4" s="140"/>
+      <c r="H4" s="140"/>
+      <c r="I4" s="141" t="s">
         <v>64</v>
       </c>
-      <c r="J4" s="146"/>
-      <c r="K4" s="146"/>
-      <c r="L4" s="147"/>
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="159"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5" s="10" t="s">
@@ -6749,12 +6734,12 @@
       <c r="H7" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="122" t="s">
+      <c r="I7" s="150" t="s">
         <v>177</v>
       </c>
-      <c r="J7" s="123"/>
-      <c r="K7" s="123"/>
-      <c r="L7" s="124"/>
+      <c r="J7" s="151"/>
+      <c r="K7" s="151"/>
+      <c r="L7" s="155"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A8" s="10" t="s">
@@ -6857,12 +6842,12 @@
       <c r="H10" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="I10" s="122" t="s">
+      <c r="I10" s="150" t="s">
         <v>192</v>
       </c>
-      <c r="J10" s="123"/>
-      <c r="K10" s="123"/>
-      <c r="L10" s="124"/>
+      <c r="J10" s="151"/>
+      <c r="K10" s="151"/>
+      <c r="L10" s="155"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A11" s="10" t="s">
@@ -6877,12 +6862,12 @@
       <c r="D11" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="148" t="s">
+      <c r="E11" s="152" t="s">
         <v>155</v>
       </c>
-      <c r="F11" s="149"/>
-      <c r="G11" s="149"/>
-      <c r="H11" s="149"/>
+      <c r="F11" s="153"/>
+      <c r="G11" s="153"/>
+      <c r="H11" s="153"/>
       <c r="I11" s="22" t="s">
         <v>181</v>
       </c>
@@ -6935,12 +6920,12 @@
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A13" s="118" t="s">
+      <c r="A13" s="133" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="119"/>
-      <c r="C13" s="119"/>
-      <c r="D13" s="120"/>
+      <c r="B13" s="134"/>
+      <c r="C13" s="134"/>
+      <c r="D13" s="135"/>
       <c r="E13" s="16" t="s">
         <v>147</v>
       </c>
@@ -6979,12 +6964,12 @@
       <c r="D14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="148" t="s">
+      <c r="E14" s="152" t="s">
         <v>158</v>
       </c>
-      <c r="F14" s="149"/>
-      <c r="G14" s="149"/>
-      <c r="H14" s="149"/>
+      <c r="F14" s="153"/>
+      <c r="G14" s="153"/>
+      <c r="H14" s="153"/>
       <c r="I14" s="22" t="s">
         <v>179</v>
       </c>
@@ -6999,12 +6984,12 @@
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A15" s="118" t="s">
+      <c r="A15" s="133" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="119"/>
-      <c r="C15" s="119"/>
-      <c r="D15" s="120"/>
+      <c r="B15" s="134"/>
+      <c r="C15" s="134"/>
+      <c r="D15" s="135"/>
       <c r="E15" s="16" t="s">
         <v>159</v>
       </c>
@@ -7017,12 +7002,12 @@
       <c r="H15" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="I15" s="122" t="s">
+      <c r="I15" s="150" t="s">
         <v>193</v>
       </c>
-      <c r="J15" s="123"/>
-      <c r="K15" s="123"/>
-      <c r="L15" s="124"/>
+      <c r="J15" s="151"/>
+      <c r="K15" s="151"/>
+      <c r="L15" s="155"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A16" s="10" t="s">
@@ -7125,20 +7110,20 @@
       <c r="H18" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="122" t="s">
+      <c r="I18" s="150" t="s">
         <v>194</v>
       </c>
-      <c r="J18" s="123"/>
-      <c r="K18" s="123"/>
-      <c r="L18" s="124"/>
+      <c r="J18" s="151"/>
+      <c r="K18" s="151"/>
+      <c r="L18" s="155"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A19" s="118" t="s">
+      <c r="A19" s="133" t="s">
         <v>113</v>
       </c>
-      <c r="B19" s="119"/>
-      <c r="C19" s="119"/>
-      <c r="D19" s="120"/>
+      <c r="B19" s="134"/>
+      <c r="C19" s="134"/>
+      <c r="D19" s="135"/>
       <c r="E19" s="16" t="s">
         <v>161</v>
       </c>
@@ -7178,12 +7163,12 @@
       <c r="D20" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E20" s="148" t="s">
+      <c r="E20" s="152" t="s">
         <v>163</v>
       </c>
-      <c r="F20" s="149"/>
-      <c r="G20" s="149"/>
-      <c r="H20" s="149"/>
+      <c r="F20" s="153"/>
+      <c r="G20" s="153"/>
+      <c r="H20" s="153"/>
       <c r="I20" s="22" t="s">
         <v>183</v>
       </c>
@@ -7298,12 +7283,12 @@
       <c r="H23" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="I23" s="122" t="s">
+      <c r="I23" s="150" t="s">
         <v>186</v>
       </c>
-      <c r="J23" s="123"/>
-      <c r="K23" s="123"/>
-      <c r="L23" s="124"/>
+      <c r="J23" s="151"/>
+      <c r="K23" s="151"/>
+      <c r="L23" s="155"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A24" s="10" t="s">
@@ -7356,12 +7341,12 @@
       <c r="D25" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E25" s="148" t="s">
+      <c r="E25" s="152" t="s">
         <v>164</v>
       </c>
-      <c r="F25" s="149"/>
-      <c r="G25" s="149"/>
-      <c r="H25" s="149"/>
+      <c r="F25" s="153"/>
+      <c r="G25" s="153"/>
+      <c r="H25" s="153"/>
       <c r="I25" s="22" t="s">
         <v>190</v>
       </c>
@@ -7376,12 +7361,12 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A26" s="118" t="s">
+      <c r="A26" s="133" t="s">
         <v>114</v>
       </c>
-      <c r="B26" s="119"/>
-      <c r="C26" s="119"/>
-      <c r="D26" s="120"/>
+      <c r="B26" s="134"/>
+      <c r="C26" s="134"/>
+      <c r="D26" s="135"/>
       <c r="E26" s="16" t="s">
         <v>165</v>
       </c>
@@ -7394,12 +7379,12 @@
       <c r="H26" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="I26" s="122" t="s">
+      <c r="I26" s="150" t="s">
         <v>195</v>
       </c>
-      <c r="J26" s="123"/>
-      <c r="K26" s="123"/>
-      <c r="L26" s="124"/>
+      <c r="J26" s="151"/>
+      <c r="K26" s="151"/>
+      <c r="L26" s="155"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A27" s="10" t="s">
@@ -7494,20 +7479,20 @@
       <c r="F29" s="17"/>
       <c r="G29" s="17"/>
       <c r="H29" s="17"/>
-      <c r="I29" s="122" t="s">
+      <c r="I29" s="150" t="s">
         <v>199</v>
       </c>
-      <c r="J29" s="123"/>
-      <c r="K29" s="123"/>
-      <c r="L29" s="124"/>
+      <c r="J29" s="151"/>
+      <c r="K29" s="151"/>
+      <c r="L29" s="155"/>
     </row>
     <row r="30" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="118" t="s">
+      <c r="A30" s="133" t="s">
         <v>119</v>
       </c>
-      <c r="B30" s="119"/>
-      <c r="C30" s="119"/>
-      <c r="D30" s="120"/>
+      <c r="B30" s="134"/>
+      <c r="C30" s="134"/>
+      <c r="D30" s="135"/>
       <c r="E30" s="19" t="s">
         <v>145</v>
       </c>
@@ -7603,12 +7588,12 @@
       <c r="D33" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I33" s="122" t="s">
+      <c r="I33" s="150" t="s">
         <v>203</v>
       </c>
-      <c r="J33" s="123"/>
-      <c r="K33" s="123"/>
-      <c r="L33" s="124"/>
+      <c r="J33" s="151"/>
+      <c r="K33" s="151"/>
+      <c r="L33" s="155"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A34" s="10" t="s">
@@ -7650,12 +7635,12 @@
       <c r="D35" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="I35" s="122" t="s">
+      <c r="I35" s="150" t="s">
         <v>363</v>
       </c>
-      <c r="J35" s="123"/>
-      <c r="K35" s="123"/>
-      <c r="L35" s="124"/>
+      <c r="J35" s="151"/>
+      <c r="K35" s="151"/>
+      <c r="L35" s="155"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A36" s="10" t="s">
@@ -7684,12 +7669,12 @@
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A37" s="118" t="s">
+      <c r="A37" s="133" t="s">
         <v>139</v>
       </c>
-      <c r="B37" s="119"/>
-      <c r="C37" s="119"/>
-      <c r="D37" s="120"/>
+      <c r="B37" s="134"/>
+      <c r="C37" s="134"/>
+      <c r="D37" s="135"/>
       <c r="I37" s="22" t="s">
         <v>365</v>
       </c>
@@ -7745,12 +7730,12 @@
       <c r="L39" s="27"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A40" s="118" t="s">
+      <c r="A40" s="133" t="s">
         <v>138</v>
       </c>
-      <c r="B40" s="119"/>
-      <c r="C40" s="119"/>
-      <c r="D40" s="120"/>
+      <c r="B40" s="134"/>
+      <c r="C40" s="134"/>
+      <c r="D40" s="135"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A41" s="10" t="s">
@@ -7809,12 +7794,12 @@
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A45" s="118" t="s">
+      <c r="A45" s="133" t="s">
         <v>136</v>
       </c>
-      <c r="B45" s="119"/>
-      <c r="C45" s="119"/>
-      <c r="D45" s="120"/>
+      <c r="B45" s="134"/>
+      <c r="C45" s="134"/>
+      <c r="D45" s="135"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A46" s="10" t="s">
@@ -7897,12 +7882,12 @@
       <c r="D51" s="12"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A52" s="118" t="s">
+      <c r="A52" s="133" t="s">
         <v>168</v>
       </c>
-      <c r="B52" s="119"/>
-      <c r="C52" s="119"/>
-      <c r="D52" s="120"/>
+      <c r="B52" s="134"/>
+      <c r="C52" s="134"/>
+      <c r="D52" s="135"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A53" s="10" t="s">
@@ -7919,12 +7904,12 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A54" s="118" t="s">
+      <c r="A54" s="133" t="s">
         <v>360</v>
       </c>
-      <c r="B54" s="119"/>
-      <c r="C54" s="119"/>
-      <c r="D54" s="120"/>
+      <c r="B54" s="134"/>
+      <c r="C54" s="134"/>
+      <c r="D54" s="135"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A55" s="10" t="s">
@@ -7976,25 +7961,45 @@
       <c r="D60" s="3"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A64" s="121"/>
-      <c r="B64" s="121"/>
-      <c r="C64" s="121"/>
-      <c r="D64" s="121"/>
+      <c r="A64" s="146"/>
+      <c r="B64" s="146"/>
+      <c r="C64" s="146"/>
+      <c r="D64" s="146"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A67" s="121"/>
-      <c r="B67" s="121"/>
-      <c r="C67" s="121"/>
-      <c r="D67" s="121"/>
+      <c r="A67" s="146"/>
+      <c r="B67" s="146"/>
+      <c r="C67" s="146"/>
+      <c r="D67" s="146"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A70" s="121"/>
-      <c r="B70" s="121"/>
-      <c r="C70" s="121"/>
-      <c r="D70" s="121"/>
+      <c r="A70" s="146"/>
+      <c r="B70" s="146"/>
+      <c r="C70" s="146"/>
+      <c r="D70" s="146"/>
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:L4"/>
     <mergeCell ref="A64:D64"/>
     <mergeCell ref="E20:H20"/>
     <mergeCell ref="A67:D67"/>
@@ -8008,26 +8013,6 @@
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="A45:D45"/>
     <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:L4"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="I7:L7"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="I35:L35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -8055,44 +8040,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="128" t="str">
+      <c r="A1" s="156" t="str">
         <f>"Icy Wilderness (total " &amp; F16 &amp; ")"</f>
         <v>Icy Wilderness (total 33988)</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="129"/>
-      <c r="J1" s="129"/>
-      <c r="K1" s="129"/>
-      <c r="L1" s="130"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="157"/>
+      <c r="J1" s="157"/>
+      <c r="K1" s="157"/>
+      <c r="L1" s="158"/>
       <c r="N1" s="2"/>
       <c r="P1" s="2"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="121" t="s">
         <v>207</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="134" t="s">
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124" t="s">
         <v>228</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="137" t="s">
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="127" t="s">
         <v>240</v>
       </c>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="139"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="129"/>
     </row>
     <row r="3" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="36" t="s">
@@ -8133,24 +8118,24 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A4" s="140" t="s">
+      <c r="A4" s="136" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="141"/>
-      <c r="C4" s="141"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="143" t="s">
+      <c r="B4" s="160"/>
+      <c r="C4" s="160"/>
+      <c r="D4" s="161"/>
+      <c r="E4" s="139" t="s">
         <v>229</v>
       </c>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144"/>
-      <c r="I4" s="145" t="s">
+      <c r="F4" s="140"/>
+      <c r="G4" s="140"/>
+      <c r="H4" s="140"/>
+      <c r="I4" s="141" t="s">
         <v>64</v>
       </c>
-      <c r="J4" s="146"/>
-      <c r="K4" s="146"/>
-      <c r="L4" s="147"/>
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="159"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5" s="10" t="s">
@@ -8229,12 +8214,12 @@
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A7" s="118" t="s">
+      <c r="A7" s="133" t="s">
         <v>217</v>
       </c>
-      <c r="B7" s="119"/>
-      <c r="C7" s="119"/>
-      <c r="D7" s="120"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="134"/>
+      <c r="D7" s="135"/>
       <c r="E7" s="30" t="s">
         <v>232</v>
       </c>
@@ -8349,12 +8334,12 @@
       <c r="D10" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="E10" s="148" t="s">
+      <c r="E10" s="152" t="s">
         <v>363</v>
       </c>
-      <c r="F10" s="149"/>
-      <c r="G10" s="149"/>
-      <c r="H10" s="149"/>
+      <c r="F10" s="153"/>
+      <c r="G10" s="153"/>
+      <c r="H10" s="153"/>
       <c r="I10" s="55" t="s">
         <v>85</v>
       </c>
@@ -8369,12 +8354,12 @@
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A11" s="118" t="s">
+      <c r="A11" s="133" t="s">
         <v>211</v>
       </c>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="120"/>
+      <c r="B11" s="134"/>
+      <c r="C11" s="134"/>
+      <c r="D11" s="135"/>
       <c r="E11" s="30" t="s">
         <v>364</v>
       </c>
@@ -8425,12 +8410,12 @@
       <c r="H12" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="I12" s="122" t="s">
+      <c r="I12" s="150" t="s">
         <v>248</v>
       </c>
-      <c r="J12" s="123"/>
-      <c r="K12" s="123"/>
-      <c r="L12" s="124"/>
+      <c r="J12" s="151"/>
+      <c r="K12" s="151"/>
+      <c r="L12" s="155"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A13" s="10" t="s">
@@ -8609,18 +8594,18 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A19" s="118" t="s">
+      <c r="A19" s="133" t="s">
         <v>273</v>
       </c>
-      <c r="B19" s="119"/>
-      <c r="C19" s="119"/>
-      <c r="D19" s="120"/>
-      <c r="I19" s="122" t="s">
+      <c r="B19" s="134"/>
+      <c r="C19" s="134"/>
+      <c r="D19" s="135"/>
+      <c r="I19" s="150" t="s">
         <v>253</v>
       </c>
-      <c r="J19" s="123"/>
-      <c r="K19" s="123"/>
-      <c r="L19" s="124"/>
+      <c r="J19" s="151"/>
+      <c r="K19" s="151"/>
+      <c r="L19" s="155"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A20" s="48" t="s">
@@ -8781,12 +8766,12 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A26" s="118" t="s">
+      <c r="A26" s="133" t="s">
         <v>527</v>
       </c>
-      <c r="B26" s="119"/>
-      <c r="C26" s="119"/>
-      <c r="D26" s="120"/>
+      <c r="B26" s="134"/>
+      <c r="C26" s="134"/>
+      <c r="D26" s="135"/>
       <c r="I26" s="55" t="s">
         <v>260</v>
       </c>
@@ -8906,18 +8891,18 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A31" s="118" t="s">
+      <c r="A31" s="133" t="s">
         <v>370</v>
       </c>
-      <c r="B31" s="119"/>
-      <c r="C31" s="119"/>
-      <c r="D31" s="120"/>
-      <c r="I31" s="122" t="s">
+      <c r="B31" s="134"/>
+      <c r="C31" s="134"/>
+      <c r="D31" s="135"/>
+      <c r="I31" s="150" t="s">
         <v>264</v>
       </c>
-      <c r="J31" s="123"/>
-      <c r="K31" s="123"/>
-      <c r="L31" s="124"/>
+      <c r="J31" s="151"/>
+      <c r="K31" s="151"/>
+      <c r="L31" s="155"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A32" s="48" t="s">
@@ -8959,20 +8944,20 @@
       <c r="D33" s="47" t="s">
         <v>528</v>
       </c>
-      <c r="I33" s="122" t="s">
+      <c r="I33" s="150" t="s">
         <v>257</v>
       </c>
-      <c r="J33" s="123"/>
-      <c r="K33" s="123"/>
-      <c r="L33" s="124"/>
+      <c r="J33" s="151"/>
+      <c r="K33" s="151"/>
+      <c r="L33" s="155"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A34" s="118" t="s">
+      <c r="A34" s="133" t="s">
         <v>275</v>
       </c>
-      <c r="B34" s="119"/>
-      <c r="C34" s="119"/>
-      <c r="D34" s="120"/>
+      <c r="B34" s="134"/>
+      <c r="C34" s="134"/>
+      <c r="D34" s="135"/>
       <c r="I34" s="55" t="s">
         <v>129</v>
       </c>
@@ -9031,12 +9016,12 @@
       <c r="L36" s="24"/>
     </row>
     <row r="37" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="118" t="s">
+      <c r="A37" s="133" t="s">
         <v>372</v>
       </c>
-      <c r="B37" s="119"/>
-      <c r="C37" s="119"/>
-      <c r="D37" s="120"/>
+      <c r="B37" s="134"/>
+      <c r="C37" s="134"/>
+      <c r="D37" s="135"/>
       <c r="I37" s="56" t="s">
         <v>239</v>
       </c>
@@ -9090,12 +9075,12 @@
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A41" s="118" t="s">
+      <c r="A41" s="133" t="s">
         <v>373</v>
       </c>
-      <c r="B41" s="119"/>
-      <c r="C41" s="119"/>
-      <c r="D41" s="120"/>
+      <c r="B41" s="134"/>
+      <c r="C41" s="134"/>
+      <c r="D41" s="135"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A42" s="48" t="s">
@@ -9126,12 +9111,12 @@
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A44" s="118" t="s">
+      <c r="A44" s="133" t="s">
         <v>374</v>
       </c>
-      <c r="B44" s="119"/>
-      <c r="C44" s="119"/>
-      <c r="D44" s="120"/>
+      <c r="B44" s="134"/>
+      <c r="C44" s="134"/>
+      <c r="D44" s="135"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A45" s="48" t="s">
@@ -9148,12 +9133,12 @@
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A46" s="118" t="s">
+      <c r="A46" s="133" t="s">
         <v>360</v>
       </c>
-      <c r="B46" s="119"/>
-      <c r="C46" s="119"/>
-      <c r="D46" s="120"/>
+      <c r="B46" s="134"/>
+      <c r="C46" s="134"/>
+      <c r="D46" s="135"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A47" s="48" t="s">
@@ -9257,39 +9242,26 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A88" s="121"/>
-      <c r="B88" s="121"/>
-      <c r="C88" s="121"/>
-      <c r="D88" s="121"/>
+      <c r="A88" s="146"/>
+      <c r="B88" s="146"/>
+      <c r="C88" s="146"/>
+      <c r="D88" s="146"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A91" s="121"/>
-      <c r="B91" s="121"/>
-      <c r="C91" s="121"/>
-      <c r="D91" s="121"/>
+      <c r="A91" s="146"/>
+      <c r="B91" s="146"/>
+      <c r="C91" s="146"/>
+      <c r="D91" s="146"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A94" s="121"/>
-      <c r="B94" s="121"/>
-      <c r="C94" s="121"/>
-      <c r="D94" s="121"/>
+      <c r="A94" s="146"/>
+      <c r="B94" s="146"/>
+      <c r="C94" s="146"/>
+      <c r="D94" s="146"/>
     </row>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="25">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:L4"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="I19:L19"/>
     <mergeCell ref="E10:H10"/>
     <mergeCell ref="A88:D88"/>
     <mergeCell ref="A91:D91"/>
@@ -9302,6 +9274,19 @@
     <mergeCell ref="A37:D37"/>
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="A44:D44"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:L4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -9337,61 +9322,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="151" t="str">
+      <c r="A1" s="118" t="str">
         <f>"Volcanic Isle (total " &amp; F30 &amp; ")"</f>
         <v>Volcanic Isle (total 48366)</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="152"/>
-      <c r="H1" s="152"/>
-      <c r="I1" s="152"/>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="152"/>
-      <c r="S1" s="152"/>
-      <c r="T1" s="153"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="120"/>
     </row>
     <row r="2" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="121" t="s">
         <v>277</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="134" t="s">
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124" t="s">
         <v>291</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="137" t="s">
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="127" t="s">
         <v>323</v>
       </c>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="139"/>
-      <c r="M2" s="159" t="s">
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="130" t="s">
         <v>327</v>
       </c>
-      <c r="N2" s="160"/>
-      <c r="O2" s="160"/>
-      <c r="P2" s="161"/>
-      <c r="Q2" s="131" t="s">
+      <c r="N2" s="131"/>
+      <c r="O2" s="131"/>
+      <c r="P2" s="132"/>
+      <c r="Q2" s="121" t="s">
         <v>350</v>
       </c>
-      <c r="R2" s="132"/>
-      <c r="S2" s="132"/>
-      <c r="T2" s="133"/>
+      <c r="R2" s="122"/>
+      <c r="S2" s="122"/>
+      <c r="T2" s="123"/>
     </row>
     <row r="3" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="s">
@@ -9456,36 +9441,36 @@
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A4" s="140" t="s">
+      <c r="A4" s="136" t="s">
         <v>278</v>
       </c>
-      <c r="B4" s="154"/>
-      <c r="C4" s="154"/>
-      <c r="D4" s="155"/>
-      <c r="E4" s="143" t="s">
+      <c r="B4" s="137"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144"/>
-      <c r="I4" s="145" t="s">
+      <c r="F4" s="140"/>
+      <c r="G4" s="140"/>
+      <c r="H4" s="140"/>
+      <c r="I4" s="141" t="s">
         <v>320</v>
       </c>
-      <c r="J4" s="146"/>
-      <c r="K4" s="146"/>
-      <c r="L4" s="146"/>
-      <c r="M4" s="162" t="s">
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="142"/>
+      <c r="M4" s="143" t="s">
         <v>329</v>
       </c>
-      <c r="N4" s="163"/>
-      <c r="O4" s="163"/>
-      <c r="P4" s="164"/>
-      <c r="Q4" s="140" t="s">
+      <c r="N4" s="144"/>
+      <c r="O4" s="144"/>
+      <c r="P4" s="145"/>
+      <c r="Q4" s="136" t="s">
         <v>349</v>
       </c>
-      <c r="R4" s="154"/>
-      <c r="S4" s="154"/>
-      <c r="T4" s="155"/>
+      <c r="R4" s="137"/>
+      <c r="S4" s="137"/>
+      <c r="T4" s="138"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A5" s="48" t="s">
@@ -9600,12 +9585,12 @@
       <c r="P6" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="Q6" s="118" t="s">
+      <c r="Q6" s="133" t="s">
         <v>352</v>
       </c>
-      <c r="R6" s="119"/>
-      <c r="S6" s="119"/>
-      <c r="T6" s="120"/>
+      <c r="R6" s="134"/>
+      <c r="S6" s="134"/>
+      <c r="T6" s="135"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A7" s="48" t="s">
@@ -9718,12 +9703,12 @@
       <c r="P8" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="Q8" s="118" t="s">
+      <c r="Q8" s="133" t="s">
         <v>353</v>
       </c>
-      <c r="R8" s="119"/>
-      <c r="S8" s="119"/>
-      <c r="T8" s="120"/>
+      <c r="R8" s="134"/>
+      <c r="S8" s="134"/>
+      <c r="T8" s="135"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A9" s="48" t="s">
@@ -9738,12 +9723,12 @@
       <c r="D9" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="148" t="s">
+      <c r="E9" s="152" t="s">
         <v>298</v>
       </c>
-      <c r="F9" s="149"/>
-      <c r="G9" s="149"/>
-      <c r="H9" s="149"/>
+      <c r="F9" s="153"/>
+      <c r="G9" s="153"/>
+      <c r="H9" s="153"/>
       <c r="I9" s="55" t="s">
         <v>313</v>
       </c>
@@ -9886,12 +9871,12 @@
         <v>2</v>
       </c>
       <c r="P11" s="68"/>
-      <c r="Q11" s="118" t="s">
+      <c r="Q11" s="133" t="s">
         <v>355</v>
       </c>
-      <c r="R11" s="119"/>
-      <c r="S11" s="119"/>
-      <c r="T11" s="120"/>
+      <c r="R11" s="134"/>
+      <c r="S11" s="134"/>
+      <c r="T11" s="135"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A12" s="48" t="s">
@@ -9930,12 +9915,12 @@
       <c r="L12" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="M12" s="156" t="s">
+      <c r="M12" s="147" t="s">
         <v>333</v>
       </c>
-      <c r="N12" s="157"/>
-      <c r="O12" s="157"/>
-      <c r="P12" s="158"/>
+      <c r="N12" s="148"/>
+      <c r="O12" s="148"/>
+      <c r="P12" s="149"/>
       <c r="Q12" s="48" t="s">
         <v>265</v>
       </c>
@@ -9962,12 +9947,12 @@
       <c r="D13" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="E13" s="148" t="s">
+      <c r="E13" s="152" t="s">
         <v>305</v>
       </c>
-      <c r="F13" s="149"/>
-      <c r="G13" s="149"/>
-      <c r="H13" s="149"/>
+      <c r="F13" s="153"/>
+      <c r="G13" s="153"/>
+      <c r="H13" s="153"/>
       <c r="I13" s="55" t="s">
         <v>318</v>
       </c>
@@ -9992,12 +9977,12 @@
       <c r="P13" s="68" t="s">
         <v>242</v>
       </c>
-      <c r="Q13" s="118" t="s">
+      <c r="Q13" s="133" t="s">
         <v>356</v>
       </c>
-      <c r="R13" s="119"/>
-      <c r="S13" s="119"/>
-      <c r="T13" s="120"/>
+      <c r="R13" s="134"/>
+      <c r="S13" s="134"/>
+      <c r="T13" s="135"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A14" s="48" t="s">
@@ -10085,12 +10070,12 @@
       <c r="H15" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="I15" s="122" t="s">
+      <c r="I15" s="150" t="s">
         <v>164</v>
       </c>
-      <c r="J15" s="123"/>
-      <c r="K15" s="123"/>
-      <c r="L15" s="123"/>
+      <c r="J15" s="151"/>
+      <c r="K15" s="151"/>
+      <c r="L15" s="151"/>
       <c r="M15" s="65" t="s">
         <v>241</v>
       </c>
@@ -10113,12 +10098,12 @@
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A16" s="118" t="s">
+      <c r="A16" s="133" t="s">
         <v>282</v>
       </c>
-      <c r="B16" s="119"/>
-      <c r="C16" s="119"/>
-      <c r="D16" s="120"/>
+      <c r="B16" s="134"/>
+      <c r="C16" s="134"/>
+      <c r="D16" s="135"/>
       <c r="E16" s="16" t="s">
         <v>302</v>
       </c>
@@ -10155,12 +10140,12 @@
       <c r="P16" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="Q16" s="118" t="s">
+      <c r="Q16" s="133" t="s">
         <v>359</v>
       </c>
-      <c r="R16" s="119"/>
-      <c r="S16" s="119"/>
-      <c r="T16" s="120"/>
+      <c r="R16" s="134"/>
+      <c r="S16" s="134"/>
+      <c r="T16" s="135"/>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A17" s="10" t="s">
@@ -10188,18 +10173,18 @@
       <c r="H17" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="I17" s="122" t="s">
+      <c r="I17" s="150" t="s">
         <v>322</v>
       </c>
-      <c r="J17" s="123"/>
-      <c r="K17" s="123"/>
-      <c r="L17" s="123"/>
-      <c r="M17" s="156" t="s">
+      <c r="J17" s="151"/>
+      <c r="K17" s="151"/>
+      <c r="L17" s="151"/>
+      <c r="M17" s="147" t="s">
         <v>340</v>
       </c>
-      <c r="N17" s="157"/>
-      <c r="O17" s="157"/>
-      <c r="P17" s="158"/>
+      <c r="N17" s="148"/>
+      <c r="O17" s="148"/>
+      <c r="P17" s="149"/>
       <c r="Q17" s="48" t="s">
         <v>265</v>
       </c>
@@ -10276,12 +10261,12 @@
       <c r="D19" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="148" t="s">
+      <c r="E19" s="152" t="s">
         <v>306</v>
       </c>
-      <c r="F19" s="149"/>
-      <c r="G19" s="149"/>
-      <c r="H19" s="149"/>
+      <c r="F19" s="153"/>
+      <c r="G19" s="153"/>
+      <c r="H19" s="153"/>
       <c r="I19" s="55" t="s">
         <v>288</v>
       </c>
@@ -10451,12 +10436,12 @@
       <c r="L22" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="M22" s="156" t="s">
+      <c r="M22" s="147" t="s">
         <v>347</v>
       </c>
-      <c r="N22" s="157"/>
-      <c r="O22" s="157"/>
-      <c r="P22" s="158"/>
+      <c r="N22" s="148"/>
+      <c r="O22" s="148"/>
+      <c r="P22" s="149"/>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A23" s="10" t="s">
@@ -10508,12 +10493,12 @@
       <c r="P23" s="68"/>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A24" s="118" t="s">
+      <c r="A24" s="133" t="s">
         <v>287</v>
       </c>
-      <c r="B24" s="119"/>
-      <c r="C24" s="119"/>
-      <c r="D24" s="120"/>
+      <c r="B24" s="134"/>
+      <c r="C24" s="134"/>
+      <c r="D24" s="135"/>
       <c r="E24" s="30" t="s">
         <v>270</v>
       </c>
@@ -10538,12 +10523,12 @@
       <c r="L24" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="M24" s="156" t="s">
+      <c r="M24" s="147" t="s">
         <v>346</v>
       </c>
-      <c r="N24" s="157"/>
-      <c r="O24" s="157"/>
-      <c r="P24" s="158"/>
+      <c r="N24" s="148"/>
+      <c r="O24" s="148"/>
+      <c r="P24" s="149"/>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A25" s="10" t="s">
@@ -10570,12 +10555,12 @@
       <c r="H25" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="I25" s="122" t="s">
+      <c r="I25" s="150" t="s">
         <v>363</v>
       </c>
-      <c r="J25" s="123"/>
-      <c r="K25" s="123"/>
-      <c r="L25" s="123"/>
+      <c r="J25" s="151"/>
+      <c r="K25" s="151"/>
+      <c r="L25" s="151"/>
       <c r="M25" s="65" t="s">
         <v>265</v>
       </c>
@@ -10660,12 +10645,12 @@
       <c r="L27" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="M27" s="156" t="s">
+      <c r="M27" s="147" t="s">
         <v>360</v>
       </c>
-      <c r="N27" s="157"/>
-      <c r="O27" s="157"/>
-      <c r="P27" s="158"/>
+      <c r="N27" s="148"/>
+      <c r="O27" s="148"/>
+      <c r="P27" s="149"/>
     </row>
     <row r="28" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="13" t="s">
@@ -10770,25 +10755,41 @@
       <c r="D65" s="3"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A69" s="121"/>
-      <c r="B69" s="121"/>
-      <c r="C69" s="121"/>
-      <c r="D69" s="121"/>
+      <c r="A69" s="146"/>
+      <c r="B69" s="146"/>
+      <c r="C69" s="146"/>
+      <c r="D69" s="146"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A72" s="121"/>
-      <c r="B72" s="121"/>
-      <c r="C72" s="121"/>
-      <c r="D72" s="121"/>
+      <c r="A72" s="146"/>
+      <c r="B72" s="146"/>
+      <c r="C72" s="146"/>
+      <c r="D72" s="146"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A75" s="121"/>
-      <c r="B75" s="121"/>
-      <c r="C75" s="121"/>
-      <c r="D75" s="121"/>
+      <c r="A75" s="146"/>
+      <c r="B75" s="146"/>
+      <c r="C75" s="146"/>
+      <c r="D75" s="146"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="Q16:T16"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="Q6:T6"/>
+    <mergeCell ref="Q8:T8"/>
+    <mergeCell ref="Q11:T11"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="M17:P17"/>
+    <mergeCell ref="M22:P22"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="M27:P27"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I17:L17"/>
     <mergeCell ref="M2:P2"/>
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="Q2:T2"/>
@@ -10805,22 +10806,6 @@
     <mergeCell ref="I4:L4"/>
     <mergeCell ref="M4:P4"/>
     <mergeCell ref="M12:P12"/>
-    <mergeCell ref="M27:P27"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="Q16:T16"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="Q4:T4"/>
-    <mergeCell ref="Q6:T6"/>
-    <mergeCell ref="Q8:T8"/>
-    <mergeCell ref="Q11:T11"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="M17:P17"/>
-    <mergeCell ref="M22:P22"/>
-    <mergeCell ref="M24:P24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -10849,44 +10834,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="128" t="str">
+      <c r="A1" s="156" t="str">
         <f>"Lost Cities (total " &amp; F30 &amp; ")"</f>
         <v>Lost Cities (total 34648)</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="129"/>
-      <c r="J1" s="129"/>
-      <c r="K1" s="129"/>
-      <c r="L1" s="130"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="157"/>
+      <c r="J1" s="157"/>
+      <c r="K1" s="157"/>
+      <c r="L1" s="158"/>
       <c r="N1" s="2"/>
       <c r="P1" s="2"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="121" t="s">
         <v>98</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="134" t="s">
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124" t="s">
         <v>146</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="137" t="s">
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="127" t="s">
         <v>170</v>
       </c>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="139"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="129"/>
     </row>
     <row r="3" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="36" t="s">
@@ -10927,24 +10912,24 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A4" s="118" t="s">
+      <c r="A4" s="133" t="s">
         <v>441</v>
       </c>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="120"/>
-      <c r="E4" s="143" t="s">
+      <c r="B4" s="134"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="139" t="s">
         <v>454</v>
       </c>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144"/>
-      <c r="I4" s="145" t="s">
+      <c r="F4" s="140"/>
+      <c r="G4" s="140"/>
+      <c r="H4" s="140"/>
+      <c r="I4" s="141" t="s">
         <v>446</v>
       </c>
-      <c r="J4" s="146"/>
-      <c r="K4" s="146"/>
-      <c r="L4" s="147"/>
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="159"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5" s="10" t="s">
@@ -11083,12 +11068,12 @@
       <c r="H8" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="I8" s="122" t="s">
+      <c r="I8" s="150" t="s">
         <v>447</v>
       </c>
-      <c r="J8" s="123"/>
-      <c r="K8" s="123"/>
-      <c r="L8" s="124"/>
+      <c r="J8" s="151"/>
+      <c r="K8" s="151"/>
+      <c r="L8" s="155"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A9" s="10" t="s">
@@ -11140,12 +11125,12 @@
       <c r="D10" s="12" t="s">
         <v>554</v>
       </c>
-      <c r="E10" s="148" t="s">
+      <c r="E10" s="152" t="s">
         <v>455</v>
       </c>
-      <c r="F10" s="149"/>
-      <c r="G10" s="149"/>
-      <c r="H10" s="150"/>
+      <c r="F10" s="153"/>
+      <c r="G10" s="153"/>
+      <c r="H10" s="154"/>
       <c r="I10" s="22" t="s">
         <v>424</v>
       </c>
@@ -11310,12 +11295,12 @@
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A15" s="118" t="s">
+      <c r="A15" s="133" t="s">
         <v>442</v>
       </c>
-      <c r="B15" s="119"/>
-      <c r="C15" s="119"/>
-      <c r="D15" s="120"/>
+      <c r="B15" s="134"/>
+      <c r="C15" s="134"/>
+      <c r="D15" s="135"/>
       <c r="E15" s="16" t="s">
         <v>265</v>
       </c>
@@ -11431,18 +11416,18 @@
       <c r="D18" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E18" s="148" t="s">
+      <c r="E18" s="152" t="s">
         <v>453</v>
       </c>
-      <c r="F18" s="149"/>
-      <c r="G18" s="149"/>
-      <c r="H18" s="150"/>
-      <c r="I18" s="122" t="s">
+      <c r="F18" s="153"/>
+      <c r="G18" s="153"/>
+      <c r="H18" s="154"/>
+      <c r="I18" s="150" t="s">
         <v>546</v>
       </c>
-      <c r="J18" s="123"/>
-      <c r="K18" s="123"/>
-      <c r="L18" s="124"/>
+      <c r="J18" s="151"/>
+      <c r="K18" s="151"/>
+      <c r="L18" s="155"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19" s="10" t="s">
@@ -11483,12 +11468,12 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="118" t="s">
+      <c r="A20" s="133" t="s">
         <v>565</v>
       </c>
-      <c r="B20" s="119"/>
-      <c r="C20" s="119"/>
-      <c r="D20" s="120"/>
+      <c r="B20" s="134"/>
+      <c r="C20" s="134"/>
+      <c r="D20" s="135"/>
       <c r="E20" s="16" t="s">
         <v>160</v>
       </c>
@@ -11577,12 +11562,12 @@
       <c r="H22" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="I22" s="122" t="s">
+      <c r="I22" s="150" t="s">
         <v>448</v>
       </c>
-      <c r="J22" s="123"/>
-      <c r="K22" s="123"/>
-      <c r="L22" s="124"/>
+      <c r="J22" s="151"/>
+      <c r="K22" s="151"/>
+      <c r="L22" s="155"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A23" s="10" t="s">
@@ -11635,12 +11620,12 @@
       <c r="D24" s="12" t="s">
         <v>554</v>
       </c>
-      <c r="E24" s="148" t="s">
+      <c r="E24" s="152" t="s">
         <v>456</v>
       </c>
-      <c r="F24" s="149"/>
-      <c r="G24" s="149"/>
-      <c r="H24" s="150"/>
+      <c r="F24" s="153"/>
+      <c r="G24" s="153"/>
+      <c r="H24" s="154"/>
       <c r="I24" s="25" t="s">
         <v>196</v>
       </c>
@@ -11718,12 +11703,12 @@
       <c r="H26" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I26" s="122" t="s">
+      <c r="I26" s="150" t="s">
         <v>449</v>
       </c>
-      <c r="J26" s="123"/>
-      <c r="K26" s="123"/>
-      <c r="L26" s="124"/>
+      <c r="J26" s="151"/>
+      <c r="K26" s="151"/>
+      <c r="L26" s="155"/>
     </row>
     <row r="27" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="10" t="s">
@@ -11845,20 +11830,20 @@
         <f>B49+F28+J33</f>
         <v>34648</v>
       </c>
-      <c r="I30" s="122" t="s">
+      <c r="I30" s="150" t="s">
         <v>450</v>
       </c>
-      <c r="J30" s="123"/>
-      <c r="K30" s="123"/>
-      <c r="L30" s="124"/>
+      <c r="J30" s="151"/>
+      <c r="K30" s="151"/>
+      <c r="L30" s="155"/>
     </row>
     <row r="31" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="118" t="s">
+      <c r="A31" s="133" t="s">
         <v>540</v>
       </c>
-      <c r="B31" s="119"/>
-      <c r="C31" s="119"/>
-      <c r="D31" s="120"/>
+      <c r="B31" s="134"/>
+      <c r="C31" s="134"/>
+      <c r="D31" s="135"/>
       <c r="I31" s="22" t="s">
         <v>549</v>
       </c>
@@ -11979,12 +11964,12 @@
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A38" s="118" t="s">
+      <c r="A38" s="133" t="s">
         <v>561</v>
       </c>
-      <c r="B38" s="119"/>
-      <c r="C38" s="119"/>
-      <c r="D38" s="120"/>
+      <c r="B38" s="134"/>
+      <c r="C38" s="134"/>
+      <c r="D38" s="135"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A39" s="10" t="s">
@@ -12086,12 +12071,12 @@
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A46" s="118" t="s">
+      <c r="A46" s="133" t="s">
         <v>445</v>
       </c>
-      <c r="B46" s="119"/>
-      <c r="C46" s="119"/>
-      <c r="D46" s="120"/>
+      <c r="B46" s="134"/>
+      <c r="C46" s="134"/>
+      <c r="D46" s="135"/>
     </row>
     <row r="47" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A47" s="13" t="s">
@@ -12137,22 +12122,22 @@
       <c r="D51" s="3"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A55" s="121"/>
-      <c r="B55" s="121"/>
-      <c r="C55" s="121"/>
-      <c r="D55" s="121"/>
+      <c r="A55" s="146"/>
+      <c r="B55" s="146"/>
+      <c r="C55" s="146"/>
+      <c r="D55" s="146"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A58" s="121"/>
-      <c r="B58" s="121"/>
-      <c r="C58" s="121"/>
-      <c r="D58" s="121"/>
+      <c r="A58" s="146"/>
+      <c r="B58" s="146"/>
+      <c r="C58" s="146"/>
+      <c r="D58" s="146"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A61" s="121"/>
-      <c r="B61" s="121"/>
-      <c r="C61" s="121"/>
-      <c r="D61" s="121"/>
+      <c r="A61" s="146"/>
+      <c r="B61" s="146"/>
+      <c r="C61" s="146"/>
+      <c r="D61" s="146"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A32:D36">
@@ -12160,20 +12145,6 @@
     <sortCondition ref="D32:D36"/>
   </sortState>
   <mergeCells count="23">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:L4"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I18:L18"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A58:D58"/>
     <mergeCell ref="A61:D61"/>
@@ -12183,6 +12154,20 @@
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A38:D38"/>
     <mergeCell ref="A46:D46"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:L4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -12210,44 +12195,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="128" t="str">
+      <c r="A1" s="156" t="str">
         <f>"Icy Wilderness (total " &amp; F10 &amp; ")"</f>
         <v>Icy Wilderness (total 35781)</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="129"/>
-      <c r="J1" s="129"/>
-      <c r="K1" s="129"/>
-      <c r="L1" s="130"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="157"/>
+      <c r="J1" s="157"/>
+      <c r="K1" s="157"/>
+      <c r="L1" s="158"/>
       <c r="N1" s="2"/>
       <c r="P1" s="2"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="121" t="s">
         <v>207</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="134" t="s">
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124" t="s">
         <v>228</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="137" t="s">
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="127" t="s">
         <v>240</v>
       </c>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="139"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="129"/>
     </row>
     <row r="3" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="36" t="s">
@@ -12288,24 +12273,24 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A4" s="140" t="s">
+      <c r="A4" s="136" t="s">
         <v>457</v>
       </c>
-      <c r="B4" s="141"/>
-      <c r="C4" s="141"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="143" t="s">
+      <c r="B4" s="160"/>
+      <c r="C4" s="160"/>
+      <c r="D4" s="161"/>
+      <c r="E4" s="139" t="s">
         <v>461</v>
       </c>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144"/>
-      <c r="I4" s="145" t="s">
+      <c r="F4" s="140"/>
+      <c r="G4" s="140"/>
+      <c r="H4" s="140"/>
+      <c r="I4" s="141" t="s">
         <v>462</v>
       </c>
-      <c r="J4" s="146"/>
-      <c r="K4" s="146"/>
-      <c r="L4" s="147"/>
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="159"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5" s="10" t="s">
@@ -12413,12 +12398,12 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="118" t="s">
+      <c r="A8" s="133" t="s">
         <v>458</v>
       </c>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="120"/>
+      <c r="B8" s="134"/>
+      <c r="C8" s="134"/>
+      <c r="D8" s="135"/>
       <c r="E8" s="53" t="s">
         <v>238</v>
       </c>
@@ -12446,7 +12431,7 @@
         <v>175</v>
       </c>
       <c r="B9" s="45">
-        <v>415</v>
+        <v>120</v>
       </c>
       <c r="C9" s="46" t="s">
         <v>49</v>
@@ -12469,13 +12454,13 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A10" s="10" t="s">
-        <v>209</v>
+        <v>577</v>
       </c>
       <c r="B10" s="45">
-        <v>130</v>
+        <v>320</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>210</v>
+        <v>575</v>
       </c>
       <c r="D10" s="47" t="s">
         <v>2</v>
@@ -12501,16 +12486,16 @@
       </c>
     </row>
     <row r="11" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="B11" s="61">
-        <v>25</v>
-      </c>
-      <c r="C11" s="78" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="79" t="s">
+      <c r="A11" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="B11" s="45">
+        <v>130</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>576</v>
+      </c>
+      <c r="D11" s="47" t="s">
         <v>2</v>
       </c>
       <c r="I11" s="56" t="s">
@@ -12550,18 +12535,18 @@
       <c r="L12" s="60"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A13" s="118" t="s">
+      <c r="A13" s="133" t="s">
         <v>459</v>
       </c>
-      <c r="B13" s="119"/>
-      <c r="C13" s="119"/>
-      <c r="D13" s="120"/>
-      <c r="I13" s="122" t="s">
+      <c r="B13" s="134"/>
+      <c r="C13" s="134"/>
+      <c r="D13" s="135"/>
+      <c r="I13" s="150" t="s">
         <v>463</v>
       </c>
-      <c r="J13" s="123"/>
-      <c r="K13" s="123"/>
-      <c r="L13" s="124"/>
+      <c r="J13" s="151"/>
+      <c r="K13" s="151"/>
+      <c r="L13" s="155"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A14" s="10" t="s">
@@ -12734,20 +12719,20 @@
         <f>D12+C20</f>
         <v>5968</v>
       </c>
-      <c r="I20" s="122" t="s">
+      <c r="I20" s="150" t="s">
         <v>464</v>
       </c>
-      <c r="J20" s="123"/>
-      <c r="K20" s="123"/>
-      <c r="L20" s="124"/>
+      <c r="J20" s="151"/>
+      <c r="K20" s="151"/>
+      <c r="L20" s="155"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A21" s="118" t="s">
+      <c r="A21" s="133" t="s">
         <v>524</v>
       </c>
-      <c r="B21" s="119"/>
-      <c r="C21" s="119"/>
-      <c r="D21" s="120"/>
+      <c r="B21" s="134"/>
+      <c r="C21" s="134"/>
+      <c r="D21" s="135"/>
       <c r="I21" s="55" t="s">
         <v>241</v>
       </c>
@@ -12946,13 +12931,13 @@
       </c>
     </row>
     <row r="29" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="125" t="str">
+      <c r="A29" s="162" t="str">
         <f>_xlfn._LONGTEXT("---------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------","-----------------------------------------")</f>
         <v>--------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------</v>
       </c>
-      <c r="B29" s="126"/>
-      <c r="C29" s="126"/>
-      <c r="D29" s="127"/>
+      <c r="B29" s="163"/>
+      <c r="C29" s="163"/>
+      <c r="D29" s="164"/>
       <c r="I29" s="56" t="s">
         <v>508</v>
       </c>
@@ -12968,12 +12953,12 @@
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A30" s="118" t="s">
+      <c r="A30" s="133" t="s">
         <v>469</v>
       </c>
-      <c r="B30" s="119"/>
-      <c r="C30" s="119"/>
-      <c r="D30" s="120"/>
+      <c r="B30" s="134"/>
+      <c r="C30" s="134"/>
+      <c r="D30" s="135"/>
       <c r="I30" s="55" t="s">
         <v>388</v>
       </c>
@@ -13000,12 +12985,12 @@
       <c r="D31" s="47" t="s">
         <v>559</v>
       </c>
-      <c r="I31" s="122" t="s">
+      <c r="I31" s="150" t="s">
         <v>468</v>
       </c>
-      <c r="J31" s="123"/>
-      <c r="K31" s="123"/>
-      <c r="L31" s="124"/>
+      <c r="J31" s="151"/>
+      <c r="K31" s="151"/>
+      <c r="L31" s="155"/>
     </row>
     <row r="32" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A32" s="80" t="s">
@@ -13058,12 +13043,12 @@
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A34" s="118" t="s">
+      <c r="A34" s="133" t="s">
         <v>470</v>
       </c>
-      <c r="B34" s="119"/>
-      <c r="C34" s="119"/>
-      <c r="D34" s="120"/>
+      <c r="B34" s="134"/>
+      <c r="C34" s="134"/>
+      <c r="D34" s="135"/>
       <c r="I34" s="55" t="s">
         <v>388</v>
       </c>
@@ -13090,12 +13075,12 @@
       <c r="D35" s="79" t="s">
         <v>559</v>
       </c>
-      <c r="I35" s="122" t="s">
+      <c r="I35" s="150" t="s">
         <v>465</v>
       </c>
-      <c r="J35" s="123"/>
-      <c r="K35" s="123"/>
-      <c r="L35" s="124"/>
+      <c r="J35" s="151"/>
+      <c r="K35" s="151"/>
+      <c r="L35" s="155"/>
     </row>
     <row r="36" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="48" t="s">
@@ -13125,12 +13110,12 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="118" t="s">
+      <c r="A37" s="133" t="s">
         <v>537</v>
       </c>
-      <c r="B37" s="119"/>
-      <c r="C37" s="119"/>
-      <c r="D37" s="120"/>
+      <c r="B37" s="134"/>
+      <c r="C37" s="134"/>
+      <c r="D37" s="135"/>
       <c r="I37" s="25" t="s">
         <v>388</v>
       </c>
@@ -13207,12 +13192,12 @@
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A42" s="118" t="s">
+      <c r="A42" s="133" t="s">
         <v>538</v>
       </c>
-      <c r="B42" s="119"/>
-      <c r="C42" s="119"/>
-      <c r="D42" s="120"/>
+      <c r="B42" s="134"/>
+      <c r="C42" s="134"/>
+      <c r="D42" s="135"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A43" s="48" t="s">
@@ -13325,22 +13310,22 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A84" s="121"/>
-      <c r="B84" s="121"/>
-      <c r="C84" s="121"/>
-      <c r="D84" s="121"/>
+      <c r="A84" s="146"/>
+      <c r="B84" s="146"/>
+      <c r="C84" s="146"/>
+      <c r="D84" s="146"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A87" s="121"/>
-      <c r="B87" s="121"/>
-      <c r="C87" s="121"/>
-      <c r="D87" s="121"/>
+      <c r="A87" s="146"/>
+      <c r="B87" s="146"/>
+      <c r="C87" s="146"/>
+      <c r="D87" s="146"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A90" s="121"/>
-      <c r="B90" s="121"/>
-      <c r="C90" s="121"/>
-      <c r="D90" s="121"/>
+      <c r="A90" s="146"/>
+      <c r="B90" s="146"/>
+      <c r="C90" s="146"/>
+      <c r="D90" s="146"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I21:L29">
@@ -13348,11 +13333,16 @@
     <sortCondition ref="L21:L29"/>
   </sortState>
   <mergeCells count="22">
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="A87:D87"/>
+    <mergeCell ref="A90:D90"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A29:D29"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:H2"/>
@@ -13360,16 +13350,11 @@
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="E4:H4"/>
     <mergeCell ref="I4:L4"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A84:D84"/>
-    <mergeCell ref="A87:D87"/>
-    <mergeCell ref="A90:D90"/>
-    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="A21:D21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -13406,61 +13391,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="151" t="str">
+      <c r="A1" s="118" t="str">
         <f>"Volcanic Isle (total " &amp; F28 &amp; ")"</f>
         <v>Volcanic Isle (total 49306)</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="152"/>
-      <c r="H1" s="152"/>
-      <c r="I1" s="152"/>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="152"/>
-      <c r="S1" s="152"/>
-      <c r="T1" s="153"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="120"/>
     </row>
     <row r="2" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="121" t="s">
         <v>277</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="134" t="s">
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124" t="s">
         <v>291</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="137" t="s">
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="127" t="s">
         <v>323</v>
       </c>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="139"/>
-      <c r="M2" s="159" t="s">
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="130" t="s">
         <v>327</v>
       </c>
-      <c r="N2" s="160"/>
-      <c r="O2" s="160"/>
-      <c r="P2" s="161"/>
-      <c r="Q2" s="131" t="s">
+      <c r="N2" s="131"/>
+      <c r="O2" s="131"/>
+      <c r="P2" s="132"/>
+      <c r="Q2" s="121" t="s">
         <v>350</v>
       </c>
-      <c r="R2" s="132"/>
-      <c r="S2" s="132"/>
-      <c r="T2" s="133"/>
+      <c r="R2" s="122"/>
+      <c r="S2" s="122"/>
+      <c r="T2" s="123"/>
     </row>
     <row r="3" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="s">
@@ -13525,36 +13510,36 @@
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A4" s="140" t="s">
+      <c r="A4" s="136" t="s">
         <v>476</v>
       </c>
-      <c r="B4" s="154"/>
-      <c r="C4" s="154"/>
-      <c r="D4" s="155"/>
-      <c r="E4" s="143" t="s">
+      <c r="B4" s="137"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="139" t="s">
         <v>479</v>
       </c>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144"/>
-      <c r="I4" s="145" t="s">
+      <c r="F4" s="140"/>
+      <c r="G4" s="140"/>
+      <c r="H4" s="140"/>
+      <c r="I4" s="141" t="s">
         <v>492</v>
       </c>
-      <c r="J4" s="146"/>
-      <c r="K4" s="146"/>
-      <c r="L4" s="146"/>
-      <c r="M4" s="162" t="s">
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="142"/>
+      <c r="M4" s="143" t="s">
         <v>486</v>
       </c>
-      <c r="N4" s="163"/>
-      <c r="O4" s="163"/>
-      <c r="P4" s="164"/>
-      <c r="Q4" s="140" t="s">
+      <c r="N4" s="144"/>
+      <c r="O4" s="144"/>
+      <c r="P4" s="145"/>
+      <c r="Q4" s="136" t="s">
         <v>491</v>
       </c>
-      <c r="R4" s="154"/>
-      <c r="S4" s="154"/>
-      <c r="T4" s="155"/>
+      <c r="R4" s="137"/>
+      <c r="S4" s="137"/>
+      <c r="T4" s="138"/>
     </row>
     <row r="5" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="48" t="s">
@@ -13727,12 +13712,12 @@
       <c r="P7" s="68" t="s">
         <v>522</v>
       </c>
-      <c r="Q7" s="118" t="s">
+      <c r="Q7" s="133" t="s">
         <v>494</v>
       </c>
-      <c r="R7" s="119"/>
-      <c r="S7" s="119"/>
-      <c r="T7" s="120"/>
+      <c r="R7" s="134"/>
+      <c r="S7" s="134"/>
+      <c r="T7" s="135"/>
     </row>
     <row r="8" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="48" t="s">
@@ -13868,12 +13853,12 @@
       <c r="D10" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="148" t="s">
+      <c r="E10" s="152" t="s">
         <v>525</v>
       </c>
-      <c r="F10" s="149"/>
-      <c r="G10" s="149"/>
-      <c r="H10" s="149"/>
+      <c r="F10" s="153"/>
+      <c r="G10" s="153"/>
+      <c r="H10" s="153"/>
       <c r="I10" s="55" t="s">
         <v>269</v>
       </c>
@@ -13946,18 +13931,18 @@
       <c r="L11" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="M11" s="156" t="s">
+      <c r="M11" s="147" t="s">
         <v>487</v>
       </c>
-      <c r="N11" s="157"/>
-      <c r="O11" s="157"/>
-      <c r="P11" s="158"/>
-      <c r="Q11" s="118" t="s">
+      <c r="N11" s="148"/>
+      <c r="O11" s="148"/>
+      <c r="P11" s="149"/>
+      <c r="Q11" s="133" t="s">
         <v>495</v>
       </c>
-      <c r="R11" s="119"/>
-      <c r="S11" s="119"/>
-      <c r="T11" s="120"/>
+      <c r="R11" s="134"/>
+      <c r="S11" s="134"/>
+      <c r="T11" s="135"/>
     </row>
     <row r="12" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="48" t="s">
@@ -14044,12 +14029,12 @@
       <c r="H13" s="32" t="s">
         <v>552</v>
       </c>
-      <c r="I13" s="122" t="s">
+      <c r="I13" s="150" t="s">
         <v>485</v>
       </c>
-      <c r="J13" s="123"/>
-      <c r="K13" s="123"/>
-      <c r="L13" s="123"/>
+      <c r="J13" s="151"/>
+      <c r="K13" s="151"/>
+      <c r="L13" s="151"/>
       <c r="M13" s="65" t="s">
         <v>330</v>
       </c>
@@ -14124,12 +14109,12 @@
       <c r="P14" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="Q14" s="118" t="s">
+      <c r="Q14" s="133" t="s">
         <v>496</v>
       </c>
-      <c r="R14" s="119"/>
-      <c r="S14" s="119"/>
-      <c r="T14" s="120"/>
+      <c r="R14" s="134"/>
+      <c r="S14" s="134"/>
+      <c r="T14" s="135"/>
     </row>
     <row r="15" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="80" t="s">
@@ -14216,18 +14201,18 @@
       <c r="H16" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="I16" s="122" t="s">
+      <c r="I16" s="150" t="s">
         <v>493</v>
       </c>
-      <c r="J16" s="123"/>
-      <c r="K16" s="123"/>
-      <c r="L16" s="123"/>
-      <c r="M16" s="156" t="s">
+      <c r="J16" s="151"/>
+      <c r="K16" s="151"/>
+      <c r="L16" s="151"/>
+      <c r="M16" s="147" t="s">
         <v>488</v>
       </c>
-      <c r="N16" s="157"/>
-      <c r="O16" s="157"/>
-      <c r="P16" s="158"/>
+      <c r="N16" s="148"/>
+      <c r="O16" s="148"/>
+      <c r="P16" s="149"/>
       <c r="Q16" s="80" t="s">
         <v>357</v>
       </c>
@@ -14242,12 +14227,12 @@
       </c>
     </row>
     <row r="17" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="118" t="s">
+      <c r="A17" s="133" t="s">
         <v>477</v>
       </c>
-      <c r="B17" s="119"/>
-      <c r="C17" s="119"/>
-      <c r="D17" s="120"/>
+      <c r="B17" s="134"/>
+      <c r="C17" s="134"/>
+      <c r="D17" s="135"/>
       <c r="E17" s="19" t="s">
         <v>265</v>
       </c>
@@ -14347,12 +14332,12 @@
       <c r="P18" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="Q18" s="118" t="s">
+      <c r="Q18" s="133" t="s">
         <v>497</v>
       </c>
-      <c r="R18" s="119"/>
-      <c r="S18" s="119"/>
-      <c r="T18" s="120"/>
+      <c r="R18" s="134"/>
+      <c r="S18" s="134"/>
+      <c r="T18" s="135"/>
     </row>
     <row r="19" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="10" t="s">
@@ -14367,12 +14352,12 @@
       <c r="D19" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="148" t="s">
+      <c r="E19" s="152" t="s">
         <v>484</v>
       </c>
-      <c r="F19" s="149"/>
-      <c r="G19" s="149"/>
-      <c r="H19" s="149"/>
+      <c r="F19" s="153"/>
+      <c r="G19" s="153"/>
+      <c r="H19" s="153"/>
       <c r="I19" s="55" t="s">
         <v>363</v>
       </c>
@@ -14570,12 +14555,12 @@
         <f>L15+K22</f>
         <v>6033</v>
       </c>
-      <c r="M22" s="156" t="s">
+      <c r="M22" s="147" t="s">
         <v>489</v>
       </c>
-      <c r="N22" s="157"/>
-      <c r="O22" s="157"/>
-      <c r="P22" s="158"/>
+      <c r="N22" s="148"/>
+      <c r="O22" s="148"/>
+      <c r="P22" s="149"/>
     </row>
     <row r="23" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="10" t="s">
@@ -14625,12 +14610,12 @@
       </c>
     </row>
     <row r="24" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="118" t="s">
+      <c r="A24" s="133" t="s">
         <v>478</v>
       </c>
-      <c r="B24" s="119"/>
-      <c r="C24" s="119"/>
-      <c r="D24" s="120"/>
+      <c r="B24" s="134"/>
+      <c r="C24" s="134"/>
+      <c r="D24" s="135"/>
       <c r="E24" s="53" t="s">
         <v>265</v>
       </c>
@@ -14718,12 +14703,12 @@
       </c>
       <c r="G26" s="20"/>
       <c r="H26" s="20"/>
-      <c r="M26" s="156" t="s">
+      <c r="M26" s="147" t="s">
         <v>490</v>
       </c>
-      <c r="N26" s="157"/>
-      <c r="O26" s="157"/>
-      <c r="P26" s="158"/>
+      <c r="N26" s="148"/>
+      <c r="O26" s="148"/>
+      <c r="P26" s="149"/>
     </row>
     <row r="27" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="76" t="s">
@@ -14880,22 +14865,22 @@
       <c r="D65" s="3"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A69" s="121"/>
-      <c r="B69" s="121"/>
-      <c r="C69" s="121"/>
-      <c r="D69" s="121"/>
+      <c r="A69" s="146"/>
+      <c r="B69" s="146"/>
+      <c r="C69" s="146"/>
+      <c r="D69" s="146"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A72" s="121"/>
-      <c r="B72" s="121"/>
-      <c r="C72" s="121"/>
-      <c r="D72" s="121"/>
+      <c r="A72" s="146"/>
+      <c r="B72" s="146"/>
+      <c r="C72" s="146"/>
+      <c r="D72" s="146"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A75" s="121"/>
-      <c r="B75" s="121"/>
-      <c r="C75" s="121"/>
-      <c r="D75" s="121"/>
+      <c r="A75" s="146"/>
+      <c r="B75" s="146"/>
+      <c r="C75" s="146"/>
+      <c r="D75" s="146"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="M17:P20">
@@ -14903,6 +14888,22 @@
     <sortCondition ref="P17:P20"/>
   </sortState>
   <mergeCells count="28">
+    <mergeCell ref="M26:P26"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="M16:P16"/>
+    <mergeCell ref="Q18:T18"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="M22:P22"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="Q11:T11"/>
+    <mergeCell ref="M11:P11"/>
+    <mergeCell ref="Q14:T14"/>
+    <mergeCell ref="I13:L13"/>
     <mergeCell ref="Q7:T7"/>
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A2:D2"/>
@@ -14915,22 +14916,6 @@
     <mergeCell ref="I4:L4"/>
     <mergeCell ref="M4:P4"/>
     <mergeCell ref="Q4:T4"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="Q11:T11"/>
-    <mergeCell ref="M11:P11"/>
-    <mergeCell ref="Q14:T14"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="Q18:T18"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="M22:P22"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="M26:P26"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A72:D72"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="M16:P16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -14959,44 +14944,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="151" t="str">
+      <c r="A1" s="118" t="str">
         <f>"Dragon Kingdom (total " &amp; F32 &amp; ")"</f>
         <v>Dragon Kingdom (total 22722)</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="152"/>
-      <c r="H1" s="152"/>
-      <c r="I1" s="152"/>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="153"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="120"/>
       <c r="N1" s="2"/>
       <c r="P1" s="2"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="121" t="s">
         <v>375</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="134" t="s">
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124" t="s">
         <v>392</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="137" t="s">
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="127" t="s">
         <v>376</v>
       </c>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="139"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="129"/>
     </row>
     <row r="3" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="s">
@@ -15037,24 +15022,24 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A4" s="140" t="s">
+      <c r="A4" s="136" t="s">
         <v>435</v>
       </c>
-      <c r="B4" s="154"/>
-      <c r="C4" s="154"/>
-      <c r="D4" s="155"/>
-      <c r="E4" s="148" t="s">
+      <c r="B4" s="137"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="152" t="s">
         <v>433</v>
       </c>
-      <c r="F4" s="149"/>
-      <c r="G4" s="149"/>
-      <c r="H4" s="150"/>
-      <c r="I4" s="122" t="s">
+      <c r="F4" s="153"/>
+      <c r="G4" s="153"/>
+      <c r="H4" s="154"/>
+      <c r="I4" s="150" t="s">
         <v>439</v>
       </c>
-      <c r="J4" s="123"/>
-      <c r="K4" s="123"/>
-      <c r="L4" s="124"/>
+      <c r="J4" s="151"/>
+      <c r="K4" s="151"/>
+      <c r="L4" s="155"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5" s="10" t="s">
@@ -15282,12 +15267,12 @@
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A11" s="118" t="s">
+      <c r="A11" s="133" t="s">
         <v>436</v>
       </c>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="120"/>
+      <c r="B11" s="134"/>
+      <c r="C11" s="134"/>
+      <c r="D11" s="135"/>
       <c r="E11" s="16" t="s">
         <v>67</v>
       </c>
@@ -15637,12 +15622,12 @@
         <v>7685</v>
       </c>
       <c r="H20" s="18"/>
-      <c r="I20" s="122" t="s">
+      <c r="I20" s="150" t="s">
         <v>440</v>
       </c>
-      <c r="J20" s="123"/>
-      <c r="K20" s="123"/>
-      <c r="L20" s="124"/>
+      <c r="J20" s="151"/>
+      <c r="K20" s="151"/>
+      <c r="L20" s="155"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A21" s="10" t="s">
@@ -15657,12 +15642,12 @@
         <f>C10+C21</f>
         <v>3253</v>
       </c>
-      <c r="E21" s="148" t="s">
+      <c r="E21" s="152" t="s">
         <v>434</v>
       </c>
-      <c r="F21" s="149"/>
-      <c r="G21" s="149"/>
-      <c r="H21" s="150"/>
+      <c r="F21" s="153"/>
+      <c r="G21" s="153"/>
+      <c r="H21" s="154"/>
       <c r="I21" s="22" t="s">
         <v>83</v>
       </c>
@@ -15677,12 +15662,12 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A22" s="118" t="s">
+      <c r="A22" s="133" t="s">
         <v>437</v>
       </c>
-      <c r="B22" s="119"/>
-      <c r="C22" s="119"/>
-      <c r="D22" s="120"/>
+      <c r="B22" s="134"/>
+      <c r="C22" s="134"/>
+      <c r="D22" s="135"/>
       <c r="E22" s="16" t="s">
         <v>397</v>
       </c>
@@ -15988,12 +15973,12 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A32" s="118" t="s">
+      <c r="A32" s="133" t="s">
         <v>438</v>
       </c>
-      <c r="B32" s="119"/>
-      <c r="C32" s="119"/>
-      <c r="D32" s="120"/>
+      <c r="B32" s="134"/>
+      <c r="C32" s="134"/>
+      <c r="D32" s="135"/>
       <c r="E32" s="1" t="s">
         <v>206</v>
       </c>
@@ -16072,6 +16057,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="I20:L20"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:H2"/>
@@ -16079,11 +16069,6 @@
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="E4:H4"/>
     <mergeCell ref="I4:L4"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="I20:L20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -16113,44 +16098,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="128" t="str">
+      <c r="A1" s="156" t="str">
         <f>"Lost Cities (total " &amp; F33 &amp; ")"</f>
         <v>Lost Cities (total 34648)</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="129"/>
-      <c r="J1" s="129"/>
-      <c r="K1" s="129"/>
-      <c r="L1" s="130"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="157"/>
+      <c r="J1" s="157"/>
+      <c r="K1" s="157"/>
+      <c r="L1" s="158"/>
       <c r="N1" s="2"/>
       <c r="P1" s="2"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="121" t="s">
         <v>98</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="134" t="s">
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124" t="s">
         <v>146</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="137" t="s">
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="127" t="s">
         <v>170</v>
       </c>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="139"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="129"/>
     </row>
     <row r="3" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="36" t="s">
@@ -16191,24 +16176,24 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A4" s="118" t="s">
+      <c r="A4" s="133" t="s">
         <v>441</v>
       </c>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="120"/>
-      <c r="E4" s="143" t="s">
+      <c r="B4" s="134"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="139" t="s">
         <v>454</v>
       </c>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144"/>
-      <c r="I4" s="145" t="s">
+      <c r="F4" s="140"/>
+      <c r="G4" s="140"/>
+      <c r="H4" s="140"/>
+      <c r="I4" s="141" t="s">
         <v>446</v>
       </c>
-      <c r="J4" s="146"/>
-      <c r="K4" s="146"/>
-      <c r="L4" s="147"/>
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="159"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5" s="10" t="s">
@@ -16347,12 +16332,12 @@
       <c r="H8" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="I8" s="122" t="s">
+      <c r="I8" s="150" t="s">
         <v>447</v>
       </c>
-      <c r="J8" s="123"/>
-      <c r="K8" s="123"/>
-      <c r="L8" s="124"/>
+      <c r="J8" s="151"/>
+      <c r="K8" s="151"/>
+      <c r="L8" s="155"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A9" s="10" t="s">
@@ -16402,12 +16387,12 @@
       <c r="D10" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="148" t="s">
+      <c r="E10" s="152" t="s">
         <v>455</v>
       </c>
-      <c r="F10" s="149"/>
-      <c r="G10" s="149"/>
-      <c r="H10" s="150"/>
+      <c r="F10" s="153"/>
+      <c r="G10" s="153"/>
+      <c r="H10" s="154"/>
       <c r="I10" s="22" t="s">
         <v>429</v>
       </c>
@@ -16687,12 +16672,12 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A18" s="118" t="s">
+      <c r="A18" s="133" t="s">
         <v>442</v>
       </c>
-      <c r="B18" s="119"/>
-      <c r="C18" s="119"/>
-      <c r="D18" s="120"/>
+      <c r="B18" s="134"/>
+      <c r="C18" s="134"/>
+      <c r="D18" s="135"/>
       <c r="E18" s="16" t="s">
         <v>388</v>
       </c>
@@ -16731,12 +16716,12 @@
       <c r="D19" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="148" t="s">
+      <c r="E19" s="152" t="s">
         <v>453</v>
       </c>
-      <c r="F19" s="149"/>
-      <c r="G19" s="149"/>
-      <c r="H19" s="150"/>
+      <c r="F19" s="153"/>
+      <c r="G19" s="153"/>
+      <c r="H19" s="154"/>
       <c r="I19" s="22" t="s">
         <v>425</v>
       </c>
@@ -16991,18 +16976,18 @@
       <c r="D26" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E26" s="148" t="s">
+      <c r="E26" s="152" t="s">
         <v>456</v>
       </c>
-      <c r="F26" s="149"/>
-      <c r="G26" s="149"/>
-      <c r="H26" s="150"/>
-      <c r="I26" s="122" t="s">
+      <c r="F26" s="153"/>
+      <c r="G26" s="153"/>
+      <c r="H26" s="154"/>
+      <c r="I26" s="150" t="s">
         <v>448</v>
       </c>
-      <c r="J26" s="123"/>
-      <c r="K26" s="123"/>
-      <c r="L26" s="124"/>
+      <c r="J26" s="151"/>
+      <c r="K26" s="151"/>
+      <c r="L26" s="155"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A27" s="10" t="s">
@@ -17119,12 +17104,12 @@
       </c>
     </row>
     <row r="30" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="118" t="s">
+      <c r="A30" s="133" t="s">
         <v>443</v>
       </c>
-      <c r="B30" s="119"/>
-      <c r="C30" s="119"/>
-      <c r="D30" s="120"/>
+      <c r="B30" s="134"/>
+      <c r="C30" s="134"/>
+      <c r="D30" s="135"/>
       <c r="E30" s="86" t="s">
         <v>388</v>
       </c>
@@ -17137,12 +17122,12 @@
         <f>H25+G30</f>
         <v>7157</v>
       </c>
-      <c r="I30" s="122" t="s">
+      <c r="I30" s="150" t="s">
         <v>449</v>
       </c>
-      <c r="J30" s="123"/>
-      <c r="K30" s="123"/>
-      <c r="L30" s="124"/>
+      <c r="J30" s="151"/>
+      <c r="K30" s="151"/>
+      <c r="L30" s="155"/>
     </row>
     <row r="31" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="10" t="s">
@@ -17278,12 +17263,12 @@
       <c r="D35" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I35" s="122" t="s">
+      <c r="I35" s="150" t="s">
         <v>450</v>
       </c>
-      <c r="J35" s="123"/>
-      <c r="K35" s="123"/>
-      <c r="L35" s="124"/>
+      <c r="J35" s="151"/>
+      <c r="K35" s="151"/>
+      <c r="L35" s="155"/>
     </row>
     <row r="36" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="10" t="s">
@@ -17390,12 +17375,12 @@
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A41" s="118" t="s">
+      <c r="A41" s="133" t="s">
         <v>444</v>
       </c>
-      <c r="B41" s="119"/>
-      <c r="C41" s="119"/>
-      <c r="D41" s="120"/>
+      <c r="B41" s="134"/>
+      <c r="C41" s="134"/>
+      <c r="D41" s="135"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A42" s="10" t="s">
@@ -17468,12 +17453,12 @@
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A47" s="118" t="s">
+      <c r="A47" s="133" t="s">
         <v>561</v>
       </c>
-      <c r="B47" s="119"/>
-      <c r="C47" s="119"/>
-      <c r="D47" s="120"/>
+      <c r="B47" s="134"/>
+      <c r="C47" s="134"/>
+      <c r="D47" s="135"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A48" s="10" t="s">
@@ -17602,12 +17587,12 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A57" s="118" t="s">
+      <c r="A57" s="133" t="s">
         <v>445</v>
       </c>
-      <c r="B57" s="119"/>
-      <c r="C57" s="119"/>
-      <c r="D57" s="120"/>
+      <c r="B57" s="134"/>
+      <c r="C57" s="134"/>
+      <c r="D57" s="135"/>
     </row>
     <row r="58" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A58" s="13" t="s">
@@ -17653,25 +17638,34 @@
       <c r="D62" s="3"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A66" s="121"/>
-      <c r="B66" s="121"/>
-      <c r="C66" s="121"/>
-      <c r="D66" s="121"/>
+      <c r="A66" s="146"/>
+      <c r="B66" s="146"/>
+      <c r="C66" s="146"/>
+      <c r="D66" s="146"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A69" s="121"/>
-      <c r="B69" s="121"/>
-      <c r="C69" s="121"/>
-      <c r="D69" s="121"/>
+      <c r="A69" s="146"/>
+      <c r="B69" s="146"/>
+      <c r="C69" s="146"/>
+      <c r="D69" s="146"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A72" s="121"/>
-      <c r="B72" s="121"/>
-      <c r="C72" s="121"/>
-      <c r="D72" s="121"/>
+      <c r="A72" s="146"/>
+      <c r="B72" s="146"/>
+      <c r="C72" s="146"/>
+      <c r="D72" s="146"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A57:D57"/>
     <mergeCell ref="I26:L26"/>
     <mergeCell ref="I8:L8"/>
     <mergeCell ref="A1:L1"/>
@@ -17685,15 +17679,6 @@
     <mergeCell ref="E19:H19"/>
     <mergeCell ref="E10:H10"/>
     <mergeCell ref="E26:H26"/>
-    <mergeCell ref="A66:D66"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A72:D72"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="A57:D57"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -17721,44 +17706,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="128" t="str">
+      <c r="A1" s="156" t="str">
         <f>"Icy Wilderness (total " &amp; F15 &amp; ")"</f>
         <v>Icy Wilderness (total 35801)</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="129"/>
-      <c r="J1" s="129"/>
-      <c r="K1" s="129"/>
-      <c r="L1" s="130"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="157"/>
+      <c r="J1" s="157"/>
+      <c r="K1" s="157"/>
+      <c r="L1" s="158"/>
       <c r="N1" s="2"/>
       <c r="P1" s="2"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="121" t="s">
         <v>207</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="134" t="s">
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124" t="s">
         <v>228</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="137" t="s">
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="127" t="s">
         <v>240</v>
       </c>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="139"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="129"/>
     </row>
     <row r="3" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="36" t="s">
@@ -17799,24 +17784,24 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A4" s="140" t="s">
+      <c r="A4" s="136" t="s">
         <v>457</v>
       </c>
-      <c r="B4" s="141"/>
-      <c r="C4" s="141"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="143" t="s">
+      <c r="B4" s="160"/>
+      <c r="C4" s="160"/>
+      <c r="D4" s="161"/>
+      <c r="E4" s="139" t="s">
         <v>461</v>
       </c>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144"/>
-      <c r="I4" s="145" t="s">
+      <c r="F4" s="140"/>
+      <c r="G4" s="140"/>
+      <c r="H4" s="140"/>
+      <c r="I4" s="141" t="s">
         <v>462</v>
       </c>
-      <c r="J4" s="146"/>
-      <c r="K4" s="146"/>
-      <c r="L4" s="147"/>
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="159"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5" s="10" t="s">
@@ -17930,12 +17915,12 @@
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A8" s="118" t="s">
+      <c r="A8" s="133" t="s">
         <v>458</v>
       </c>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="120"/>
+      <c r="B8" s="134"/>
+      <c r="C8" s="134"/>
+      <c r="D8" s="135"/>
       <c r="E8" s="30" t="s">
         <v>233</v>
       </c>
@@ -18108,12 +18093,12 @@
       <c r="L12" s="60"/>
     </row>
     <row r="13" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="118" t="s">
+      <c r="A13" s="133" t="s">
         <v>459</v>
       </c>
-      <c r="B13" s="119"/>
-      <c r="C13" s="119"/>
-      <c r="D13" s="120"/>
+      <c r="B13" s="134"/>
+      <c r="C13" s="134"/>
+      <c r="D13" s="135"/>
       <c r="E13" s="53" t="s">
         <v>238</v>
       </c>
@@ -18123,12 +18108,12 @@
       </c>
       <c r="G13" s="20"/>
       <c r="H13" s="20"/>
-      <c r="I13" s="122" t="s">
+      <c r="I13" s="150" t="s">
         <v>463</v>
       </c>
-      <c r="J13" s="123"/>
-      <c r="K13" s="123"/>
-      <c r="L13" s="124"/>
+      <c r="J13" s="151"/>
+      <c r="K13" s="151"/>
+      <c r="L13" s="155"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A14" s="10" t="s">
@@ -18335,12 +18320,12 @@
       <c r="D21" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="I21" s="122" t="s">
+      <c r="I21" s="150" t="s">
         <v>464</v>
       </c>
-      <c r="J21" s="123"/>
-      <c r="K21" s="123"/>
-      <c r="L21" s="124"/>
+      <c r="J21" s="151"/>
+      <c r="K21" s="151"/>
+      <c r="L21" s="155"/>
     </row>
     <row r="22" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="13" t="s">
@@ -18396,12 +18381,12 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A24" s="118" t="s">
+      <c r="A24" s="133" t="s">
         <v>460</v>
       </c>
-      <c r="B24" s="119"/>
-      <c r="C24" s="119"/>
-      <c r="D24" s="120"/>
+      <c r="B24" s="134"/>
+      <c r="C24" s="134"/>
+      <c r="D24" s="135"/>
       <c r="I24" s="55" t="s">
         <v>245</v>
       </c>
@@ -18599,13 +18584,13 @@
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A32" s="125" t="str">
+      <c r="A32" s="162" t="str">
         <f>_xlfn._LONGTEXT("---------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------","---------------------")</f>
         <v>------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------</v>
       </c>
-      <c r="B32" s="126"/>
-      <c r="C32" s="126"/>
-      <c r="D32" s="127"/>
+      <c r="B32" s="163"/>
+      <c r="C32" s="163"/>
+      <c r="D32" s="164"/>
       <c r="I32" s="55" t="s">
         <v>263</v>
       </c>
@@ -18620,12 +18605,12 @@
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A33" s="118" t="s">
+      <c r="A33" s="133" t="s">
         <v>469</v>
       </c>
-      <c r="B33" s="119"/>
-      <c r="C33" s="119"/>
-      <c r="D33" s="120"/>
+      <c r="B33" s="134"/>
+      <c r="C33" s="134"/>
+      <c r="D33" s="135"/>
       <c r="I33" s="55" t="s">
         <v>498</v>
       </c>
@@ -18704,12 +18689,12 @@
       <c r="D36" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="I36" s="122" t="s">
+      <c r="I36" s="150" t="s">
         <v>468</v>
       </c>
-      <c r="J36" s="123"/>
-      <c r="K36" s="123"/>
-      <c r="L36" s="124"/>
+      <c r="J36" s="151"/>
+      <c r="K36" s="151"/>
+      <c r="L36" s="155"/>
     </row>
     <row r="37" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="80" t="s">
@@ -18761,12 +18746,12 @@
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A39" s="118" t="s">
+      <c r="A39" s="133" t="s">
         <v>470</v>
       </c>
-      <c r="B39" s="119"/>
-      <c r="C39" s="119"/>
-      <c r="D39" s="120"/>
+      <c r="B39" s="134"/>
+      <c r="C39" s="134"/>
+      <c r="D39" s="135"/>
       <c r="I39" s="55" t="s">
         <v>388</v>
       </c>
@@ -18793,12 +18778,12 @@
       <c r="D40" s="47" t="s">
         <v>528</v>
       </c>
-      <c r="I40" s="122" t="s">
+      <c r="I40" s="150" t="s">
         <v>465</v>
       </c>
-      <c r="J40" s="123"/>
-      <c r="K40" s="123"/>
-      <c r="L40" s="124"/>
+      <c r="J40" s="151"/>
+      <c r="K40" s="151"/>
+      <c r="L40" s="155"/>
     </row>
     <row r="41" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A41" s="80" t="s">
@@ -18851,12 +18836,12 @@
       <c r="L42" s="27"/>
     </row>
     <row r="43" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="118" t="s">
+      <c r="A43" s="133" t="s">
         <v>472</v>
       </c>
-      <c r="B43" s="119"/>
-      <c r="C43" s="119"/>
-      <c r="D43" s="120"/>
+      <c r="B43" s="134"/>
+      <c r="C43" s="134"/>
+      <c r="D43" s="135"/>
       <c r="I43" s="56" t="s">
         <v>239</v>
       </c>
@@ -18938,12 +18923,12 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A49" s="118" t="s">
+      <c r="A49" s="133" t="s">
         <v>471</v>
       </c>
-      <c r="B49" s="119"/>
-      <c r="C49" s="119"/>
-      <c r="D49" s="120"/>
+      <c r="B49" s="134"/>
+      <c r="C49" s="134"/>
+      <c r="D49" s="135"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A50" s="48" t="s">
@@ -19002,12 +18987,12 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A54" s="118" t="s">
+      <c r="A54" s="133" t="s">
         <v>473</v>
       </c>
-      <c r="B54" s="119"/>
-      <c r="C54" s="119"/>
-      <c r="D54" s="120"/>
+      <c r="B54" s="134"/>
+      <c r="C54" s="134"/>
+      <c r="D54" s="135"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A55" s="48" t="s">
@@ -19131,32 +19116,31 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A97" s="121"/>
-      <c r="B97" s="121"/>
-      <c r="C97" s="121"/>
-      <c r="D97" s="121"/>
+      <c r="A97" s="146"/>
+      <c r="B97" s="146"/>
+      <c r="C97" s="146"/>
+      <c r="D97" s="146"/>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A100" s="121"/>
-      <c r="B100" s="121"/>
-      <c r="C100" s="121"/>
-      <c r="D100" s="121"/>
+      <c r="A100" s="146"/>
+      <c r="B100" s="146"/>
+      <c r="C100" s="146"/>
+      <c r="D100" s="146"/>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A103" s="121"/>
-      <c r="B103" s="121"/>
-      <c r="C103" s="121"/>
-      <c r="D103" s="121"/>
+      <c r="A103" s="146"/>
+      <c r="B103" s="146"/>
+      <c r="C103" s="146"/>
+      <c r="D103" s="146"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:L4"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A39:D39"/>
     <mergeCell ref="I40:L40"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="A49:D49"/>
@@ -19167,12 +19151,13 @@
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="I21:L21"/>
     <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A97:D97"/>
-    <mergeCell ref="A100:D100"/>
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:L4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19209,61 +19194,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="151" t="str">
+      <c r="A1" s="118" t="str">
         <f>"Volcanic Isle (total " &amp; F33 &amp; ")"</f>
         <v>Volcanic Isle (total 49306)</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="152"/>
-      <c r="H1" s="152"/>
-      <c r="I1" s="152"/>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="152"/>
-      <c r="S1" s="152"/>
-      <c r="T1" s="153"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="120"/>
     </row>
     <row r="2" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="121" t="s">
         <v>277</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="134" t="s">
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124" t="s">
         <v>291</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="137" t="s">
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="127" t="s">
         <v>323</v>
       </c>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="139"/>
-      <c r="M2" s="159" t="s">
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="130" t="s">
         <v>327</v>
       </c>
-      <c r="N2" s="160"/>
-      <c r="O2" s="160"/>
-      <c r="P2" s="161"/>
-      <c r="Q2" s="131" t="s">
+      <c r="N2" s="131"/>
+      <c r="O2" s="131"/>
+      <c r="P2" s="132"/>
+      <c r="Q2" s="121" t="s">
         <v>350</v>
       </c>
-      <c r="R2" s="132"/>
-      <c r="S2" s="132"/>
-      <c r="T2" s="133"/>
+      <c r="R2" s="122"/>
+      <c r="S2" s="122"/>
+      <c r="T2" s="123"/>
     </row>
     <row r="3" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="s">
@@ -19328,36 +19313,36 @@
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A4" s="140" t="s">
+      <c r="A4" s="136" t="s">
         <v>476</v>
       </c>
-      <c r="B4" s="154"/>
-      <c r="C4" s="154"/>
-      <c r="D4" s="155"/>
-      <c r="E4" s="143" t="s">
+      <c r="B4" s="137"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="139" t="s">
         <v>479</v>
       </c>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144"/>
-      <c r="I4" s="145" t="s">
+      <c r="F4" s="140"/>
+      <c r="G4" s="140"/>
+      <c r="H4" s="140"/>
+      <c r="I4" s="141" t="s">
         <v>492</v>
       </c>
-      <c r="J4" s="146"/>
-      <c r="K4" s="146"/>
-      <c r="L4" s="146"/>
-      <c r="M4" s="162" t="s">
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="142"/>
+      <c r="M4" s="143" t="s">
         <v>486</v>
       </c>
-      <c r="N4" s="163"/>
-      <c r="O4" s="163"/>
-      <c r="P4" s="164"/>
-      <c r="Q4" s="140" t="s">
+      <c r="N4" s="144"/>
+      <c r="O4" s="144"/>
+      <c r="P4" s="145"/>
+      <c r="Q4" s="136" t="s">
         <v>491</v>
       </c>
-      <c r="R4" s="154"/>
-      <c r="S4" s="154"/>
-      <c r="T4" s="155"/>
+      <c r="R4" s="137"/>
+      <c r="S4" s="137"/>
+      <c r="T4" s="138"/>
     </row>
     <row r="5" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="48" t="s">
@@ -19531,12 +19516,12 @@
       <c r="P7" s="68" t="s">
         <v>331</v>
       </c>
-      <c r="Q7" s="118" t="s">
+      <c r="Q7" s="133" t="s">
         <v>494</v>
       </c>
-      <c r="R7" s="119"/>
-      <c r="S7" s="119"/>
-      <c r="T7" s="120"/>
+      <c r="R7" s="134"/>
+      <c r="S7" s="134"/>
+      <c r="T7" s="135"/>
     </row>
     <row r="8" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="48" t="s">
@@ -19672,12 +19657,12 @@
       <c r="D10" s="47" t="s">
         <v>242</v>
       </c>
-      <c r="E10" s="148" t="s">
+      <c r="E10" s="152" t="s">
         <v>483</v>
       </c>
-      <c r="F10" s="149"/>
-      <c r="G10" s="149"/>
-      <c r="H10" s="149"/>
+      <c r="F10" s="153"/>
+      <c r="G10" s="153"/>
+      <c r="H10" s="153"/>
       <c r="I10" s="55" t="s">
         <v>314</v>
       </c>
@@ -19761,12 +19746,12 @@
         <v>1125</v>
       </c>
       <c r="P11" s="68"/>
-      <c r="Q11" s="118" t="s">
+      <c r="Q11" s="133" t="s">
         <v>495</v>
       </c>
-      <c r="R11" s="119"/>
-      <c r="S11" s="119"/>
-      <c r="T11" s="120"/>
+      <c r="R11" s="134"/>
+      <c r="S11" s="134"/>
+      <c r="T11" s="135"/>
     </row>
     <row r="12" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="48" t="s">
@@ -19805,12 +19790,12 @@
       <c r="L12" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="M12" s="156" t="s">
+      <c r="M12" s="147" t="s">
         <v>487</v>
       </c>
-      <c r="N12" s="157"/>
-      <c r="O12" s="157"/>
-      <c r="P12" s="158"/>
+      <c r="N12" s="148"/>
+      <c r="O12" s="148"/>
+      <c r="P12" s="149"/>
       <c r="Q12" s="80" t="s">
         <v>265</v>
       </c>
@@ -19935,12 +19920,12 @@
       <c r="P14" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="Q14" s="118" t="s">
+      <c r="Q14" s="133" t="s">
         <v>496</v>
       </c>
-      <c r="R14" s="119"/>
-      <c r="S14" s="119"/>
-      <c r="T14" s="120"/>
+      <c r="R14" s="134"/>
+      <c r="S14" s="134"/>
+      <c r="T14" s="135"/>
     </row>
     <row r="15" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="80" t="s">
@@ -20024,12 +20009,12 @@
       <c r="H16" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="122" t="s">
+      <c r="I16" s="150" t="s">
         <v>485</v>
       </c>
-      <c r="J16" s="123"/>
-      <c r="K16" s="123"/>
-      <c r="L16" s="123"/>
+      <c r="J16" s="151"/>
+      <c r="K16" s="151"/>
+      <c r="L16" s="151"/>
       <c r="M16" s="97" t="s">
         <v>335</v>
       </c>
@@ -20056,12 +20041,12 @@
       </c>
     </row>
     <row r="17" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="118" t="s">
+      <c r="A17" s="133" t="s">
         <v>477</v>
       </c>
-      <c r="B17" s="119"/>
-      <c r="C17" s="119"/>
-      <c r="D17" s="120"/>
+      <c r="B17" s="134"/>
+      <c r="C17" s="134"/>
+      <c r="D17" s="135"/>
       <c r="E17" s="16" t="s">
         <v>303</v>
       </c>
@@ -20149,18 +20134,18 @@
         <f>K15+K18</f>
         <v>2047</v>
       </c>
-      <c r="M18" s="156" t="s">
+      <c r="M18" s="147" t="s">
         <v>488</v>
       </c>
-      <c r="N18" s="157"/>
-      <c r="O18" s="157"/>
-      <c r="P18" s="158"/>
-      <c r="Q18" s="118" t="s">
+      <c r="N18" s="148"/>
+      <c r="O18" s="148"/>
+      <c r="P18" s="149"/>
+      <c r="Q18" s="133" t="s">
         <v>497</v>
       </c>
-      <c r="R18" s="119"/>
-      <c r="S18" s="119"/>
-      <c r="T18" s="120"/>
+      <c r="R18" s="134"/>
+      <c r="S18" s="134"/>
+      <c r="T18" s="135"/>
     </row>
     <row r="19" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="10" t="s">
@@ -20187,12 +20172,12 @@
       <c r="H19" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="I19" s="122" t="s">
+      <c r="I19" s="150" t="s">
         <v>493</v>
       </c>
-      <c r="J19" s="123"/>
-      <c r="K19" s="123"/>
-      <c r="L19" s="123"/>
+      <c r="J19" s="151"/>
+      <c r="K19" s="151"/>
+      <c r="L19" s="151"/>
       <c r="M19" s="65" t="s">
         <v>341</v>
       </c>
@@ -20348,12 +20333,12 @@
       <c r="D22" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="E22" s="148" t="s">
+      <c r="E22" s="152" t="s">
         <v>484</v>
       </c>
-      <c r="F22" s="149"/>
-      <c r="G22" s="149"/>
-      <c r="H22" s="149"/>
+      <c r="F22" s="153"/>
+      <c r="G22" s="153"/>
+      <c r="H22" s="153"/>
       <c r="I22" s="55" t="s">
         <v>288</v>
       </c>
@@ -20464,12 +20449,12 @@
       <c r="L24" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="M24" s="156" t="s">
+      <c r="M24" s="147" t="s">
         <v>489</v>
       </c>
-      <c r="N24" s="157"/>
-      <c r="O24" s="157"/>
-      <c r="P24" s="158"/>
+      <c r="N24" s="148"/>
+      <c r="O24" s="148"/>
+      <c r="P24" s="149"/>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A25" s="10" t="s">
@@ -20522,12 +20507,12 @@
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A26" s="118" t="s">
+      <c r="A26" s="133" t="s">
         <v>478</v>
       </c>
-      <c r="B26" s="119"/>
-      <c r="C26" s="119"/>
-      <c r="D26" s="120"/>
+      <c r="B26" s="134"/>
+      <c r="C26" s="134"/>
+      <c r="D26" s="135"/>
       <c r="E26" s="30" t="s">
         <v>288</v>
       </c>
@@ -20703,12 +20688,12 @@
         <f>L18+K29</f>
         <v>6033</v>
       </c>
-      <c r="M29" s="156" t="s">
+      <c r="M29" s="147" t="s">
         <v>490</v>
       </c>
-      <c r="N29" s="157"/>
-      <c r="O29" s="157"/>
-      <c r="P29" s="158"/>
+      <c r="N29" s="148"/>
+      <c r="O29" s="148"/>
+      <c r="P29" s="149"/>
     </row>
     <row r="30" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="13" t="s">
@@ -20828,37 +20813,25 @@
       <c r="D67" s="3"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A71" s="121"/>
-      <c r="B71" s="121"/>
-      <c r="C71" s="121"/>
-      <c r="D71" s="121"/>
+      <c r="A71" s="146"/>
+      <c r="B71" s="146"/>
+      <c r="C71" s="146"/>
+      <c r="D71" s="146"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A74" s="121"/>
-      <c r="B74" s="121"/>
-      <c r="C74" s="121"/>
-      <c r="D74" s="121"/>
+      <c r="A74" s="146"/>
+      <c r="B74" s="146"/>
+      <c r="C74" s="146"/>
+      <c r="D74" s="146"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A77" s="121"/>
-      <c r="B77" s="121"/>
-      <c r="C77" s="121"/>
-      <c r="D77" s="121"/>
+      <c r="A77" s="146"/>
+      <c r="B77" s="146"/>
+      <c r="C77" s="146"/>
+      <c r="D77" s="146"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="Q2:T2"/>
-    <mergeCell ref="Q14:T14"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:L4"/>
-    <mergeCell ref="M4:P4"/>
-    <mergeCell ref="Q4:T4"/>
     <mergeCell ref="A74:D74"/>
     <mergeCell ref="A77:D77"/>
     <mergeCell ref="Q7:T7"/>
@@ -20875,6 +20848,18 @@
     <mergeCell ref="E22:H22"/>
     <mergeCell ref="M12:P12"/>
     <mergeCell ref="E10:H10"/>
+    <mergeCell ref="Q14:T14"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:L4"/>
+    <mergeCell ref="M4:P4"/>
+    <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="Q2:T2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20902,44 +20887,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="151" t="str">
+      <c r="A1" s="118" t="str">
         <f>"Dragon Kingdom (total " &amp; F36 &amp; ")"</f>
         <v>Dragon Kingdom (total 21947)</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="152"/>
-      <c r="H1" s="152"/>
-      <c r="I1" s="152"/>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="153"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="120"/>
       <c r="N1" s="2"/>
       <c r="P1" s="2"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="121" t="s">
         <v>375</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="134" t="s">
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124" t="s">
         <v>367</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="137" t="s">
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="127" t="s">
         <v>376</v>
       </c>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="139"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="129"/>
     </row>
     <row r="3" spans="1:18" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="s">
@@ -20980,24 +20965,24 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A4" s="140" t="s">
+      <c r="A4" s="136" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="154"/>
-      <c r="C4" s="154"/>
-      <c r="D4" s="155"/>
-      <c r="E4" s="148" t="s">
+      <c r="B4" s="137"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="152" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="149"/>
-      <c r="G4" s="149"/>
-      <c r="H4" s="150"/>
-      <c r="I4" s="122" t="s">
+      <c r="F4" s="153"/>
+      <c r="G4" s="153"/>
+      <c r="H4" s="154"/>
+      <c r="I4" s="150" t="s">
         <v>64</v>
       </c>
-      <c r="J4" s="123"/>
-      <c r="K4" s="123"/>
-      <c r="L4" s="124"/>
+      <c r="J4" s="151"/>
+      <c r="K4" s="151"/>
+      <c r="L4" s="155"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5" s="10" t="s">
@@ -21152,12 +21137,12 @@
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A9" s="118" t="s">
+      <c r="A9" s="133" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="120"/>
+      <c r="B9" s="134"/>
+      <c r="C9" s="134"/>
+      <c r="D9" s="135"/>
       <c r="E9" s="16" t="s">
         <v>53</v>
       </c>
@@ -21222,12 +21207,12 @@
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A11" s="118" t="s">
+      <c r="A11" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="120"/>
+      <c r="B11" s="134"/>
+      <c r="C11" s="134"/>
+      <c r="D11" s="135"/>
       <c r="E11" s="16" t="s">
         <v>67</v>
       </c>
@@ -21278,12 +21263,12 @@
       <c r="H12" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="I12" s="122" t="s">
+      <c r="I12" s="150" t="s">
         <v>75</v>
       </c>
-      <c r="J12" s="123"/>
-      <c r="K12" s="123"/>
-      <c r="L12" s="124"/>
+      <c r="J12" s="151"/>
+      <c r="K12" s="151"/>
+      <c r="L12" s="155"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A13" s="10" t="s">
@@ -21336,12 +21321,12 @@
       <c r="D14" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="148" t="s">
+      <c r="E14" s="152" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="149"/>
-      <c r="G14" s="149"/>
-      <c r="H14" s="150"/>
+      <c r="F14" s="153"/>
+      <c r="G14" s="153"/>
+      <c r="H14" s="154"/>
       <c r="I14" s="22" t="s">
         <v>74</v>
       </c>
@@ -21356,12 +21341,12 @@
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A15" s="118" t="s">
+      <c r="A15" s="133" t="s">
         <v>366</v>
       </c>
-      <c r="B15" s="119"/>
-      <c r="C15" s="119"/>
-      <c r="D15" s="120"/>
+      <c r="B15" s="134"/>
+      <c r="C15" s="134"/>
+      <c r="D15" s="135"/>
       <c r="E15" s="16" t="s">
         <v>45</v>
       </c>
@@ -21374,12 +21359,12 @@
       <c r="H15" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="122" t="s">
+      <c r="I15" s="150" t="s">
         <v>81</v>
       </c>
-      <c r="J15" s="123"/>
-      <c r="K15" s="123"/>
-      <c r="L15" s="124"/>
+      <c r="J15" s="151"/>
+      <c r="K15" s="151"/>
+      <c r="L15" s="155"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A16" s="10" t="s">
@@ -21432,12 +21417,12 @@
       <c r="D17" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="148" t="s">
+      <c r="E17" s="152" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="149"/>
-      <c r="G17" s="149"/>
-      <c r="H17" s="150"/>
+      <c r="F17" s="153"/>
+      <c r="G17" s="153"/>
+      <c r="H17" s="154"/>
       <c r="I17" s="22" t="s">
         <v>84</v>
       </c>
@@ -21540,12 +21525,12 @@
       <c r="D20" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="148" t="s">
+      <c r="E20" s="152" t="s">
         <v>55</v>
       </c>
-      <c r="F20" s="149"/>
-      <c r="G20" s="149"/>
-      <c r="H20" s="150"/>
+      <c r="F20" s="153"/>
+      <c r="G20" s="153"/>
+      <c r="H20" s="154"/>
       <c r="I20" s="22" t="s">
         <v>87</v>
       </c>
@@ -21560,12 +21545,12 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A21" s="118" t="s">
+      <c r="A21" s="133" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="119"/>
-      <c r="C21" s="119"/>
-      <c r="D21" s="120"/>
+      <c r="B21" s="134"/>
+      <c r="C21" s="134"/>
+      <c r="D21" s="135"/>
       <c r="E21" s="16" t="s">
         <v>56</v>
       </c>
@@ -21578,12 +21563,12 @@
       <c r="H21" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="I21" s="122" t="s">
+      <c r="I21" s="150" t="s">
         <v>91</v>
       </c>
-      <c r="J21" s="123"/>
-      <c r="K21" s="123"/>
-      <c r="L21" s="124"/>
+      <c r="J21" s="151"/>
+      <c r="K21" s="151"/>
+      <c r="L21" s="155"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A22" s="10" t="s">
@@ -21701,24 +21686,24 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A25" s="118" t="s">
+      <c r="A25" s="133" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="119"/>
-      <c r="C25" s="119"/>
-      <c r="D25" s="120"/>
-      <c r="E25" s="148" t="s">
+      <c r="B25" s="134"/>
+      <c r="C25" s="134"/>
+      <c r="D25" s="135"/>
+      <c r="E25" s="152" t="s">
         <v>60</v>
       </c>
-      <c r="F25" s="149"/>
-      <c r="G25" s="149"/>
-      <c r="H25" s="150"/>
-      <c r="I25" s="122" t="s">
+      <c r="F25" s="153"/>
+      <c r="G25" s="153"/>
+      <c r="H25" s="154"/>
+      <c r="I25" s="150" t="s">
         <v>363</v>
       </c>
-      <c r="J25" s="123"/>
-      <c r="K25" s="123"/>
-      <c r="L25" s="124"/>
+      <c r="J25" s="151"/>
+      <c r="K25" s="151"/>
+      <c r="L25" s="155"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A26" s="10" t="s">
@@ -21797,18 +21782,18 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A28" s="118" t="s">
+      <c r="A28" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="119"/>
-      <c r="C28" s="119"/>
-      <c r="D28" s="120"/>
-      <c r="E28" s="148" t="s">
+      <c r="B28" s="134"/>
+      <c r="C28" s="134"/>
+      <c r="D28" s="135"/>
+      <c r="E28" s="152" t="s">
         <v>62</v>
       </c>
-      <c r="F28" s="149"/>
-      <c r="G28" s="149"/>
-      <c r="H28" s="150"/>
+      <c r="F28" s="153"/>
+      <c r="G28" s="153"/>
+      <c r="H28" s="154"/>
       <c r="I28" s="22"/>
       <c r="J28" s="23"/>
       <c r="K28" s="23"/>
@@ -21862,20 +21847,20 @@
       <c r="D30" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E30" s="148" t="s">
+      <c r="E30" s="152" t="s">
         <v>360</v>
       </c>
-      <c r="F30" s="149"/>
-      <c r="G30" s="149"/>
-      <c r="H30" s="150"/>
+      <c r="F30" s="153"/>
+      <c r="G30" s="153"/>
+      <c r="H30" s="154"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A31" s="118" t="s">
+      <c r="A31" s="133" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="119"/>
-      <c r="C31" s="119"/>
-      <c r="D31" s="120"/>
+      <c r="B31" s="134"/>
+      <c r="C31" s="134"/>
+      <c r="D31" s="135"/>
       <c r="E31" s="16" t="s">
         <v>361</v>
       </c>
@@ -21971,6 +21956,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="I4:L4"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I15:L15"/>
     <mergeCell ref="I21:L21"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="E2:H2"/>
@@ -21987,14 +21980,6 @@
     <mergeCell ref="A28:D28"/>
     <mergeCell ref="E30:H30"/>
     <mergeCell ref="I25:L25"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="I4:L4"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I15:L15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/worlds/spyro_aht/setup/Gem Research.xlsx
+++ b/worlds/spyro_aht/setup/Gem Research.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean\Downloads\Archipelago Stuff\.apworlds\PhoenixAP\worlds\spyro_aht\setup\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean\Downloads\Archipelago Stuff\apworlds\PhoenixAP\worlds\spyro_aht\setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231CD9C6-0017-4852-8B2E-17C12C05CF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A528B702-1771-4E26-A2C5-616CCEBB35D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="697" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="697" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="New Gems (simplified per-rule)" sheetId="14" r:id="rId1"/>
@@ -2174,9 +2174,6 @@
     <t>frozen gem blocks via exploding arrows</t>
   </si>
   <si>
-    <t>steel traps via exploding arrows</t>
-  </si>
-  <si>
     <t>armored chests</t>
   </si>
   <si>
@@ -2436,6 +2433,9 @@
   </si>
   <si>
     <t>OTHER</t>
+  </si>
+  <si>
+    <t>[enemy] steel traps via exploding arrows</t>
   </si>
 </sst>
 </file>
@@ -13950,7 +13950,7 @@
     </row>
     <row r="804" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A804" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B804" s="1">
         <v>16153</v>
@@ -13958,7 +13958,7 @@
     </row>
     <row r="805" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A805" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B805" s="1">
         <f>B802-B803-B804</f>
@@ -14082,7 +14082,7 @@
         <v>396</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>21</v>
@@ -14138,7 +14138,7 @@
         <v>335</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>21</v>
@@ -14167,7 +14167,7 @@
         <v>215</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>21</v>
@@ -14182,7 +14182,7 @@
         <v>286</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>21</v>
@@ -14225,7 +14225,7 @@
         <v>451</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>21</v>
@@ -14399,7 +14399,7 @@
         <v>260</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>50</v>
@@ -14498,7 +14498,7 @@
         <v>205</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>21</v>
@@ -14582,7 +14582,7 @@
         <v>175</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>21</v>
@@ -14835,7 +14835,7 @@
         <v>105</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>21</v>
@@ -15122,7 +15122,7 @@
         <v>223</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>21</v>
@@ -15234,7 +15234,7 @@
         <v>330</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>21</v>
@@ -15305,7 +15305,7 @@
         <v>994</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>21</v>
@@ -15319,7 +15319,7 @@
         <v>275</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>21</v>
@@ -15717,7 +15717,7 @@
         <v>175</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>36</v>
@@ -15773,7 +15773,7 @@
         <v>40</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>50</v>
@@ -15788,7 +15788,7 @@
         <v>303</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>21</v>
@@ -15858,7 +15858,7 @@
         <v>2020</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>68</v>
@@ -15872,7 +15872,7 @@
         <v>1050</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>226</v>
@@ -15915,7 +15915,7 @@
         <v>525</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>21</v>
@@ -15985,7 +15985,7 @@
         <v>388</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>228</v>
@@ -16056,7 +16056,7 @@
         <v>115</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>50</v>
@@ -16154,7 +16154,7 @@
         <v>120</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>50</v>
@@ -16371,7 +16371,7 @@
         <v>180</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>21</v>
@@ -16554,7 +16554,7 @@
         <v>755</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D186" s="1" t="s">
         <v>21</v>
@@ -16610,7 +16610,7 @@
         <v>85</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>21</v>
@@ -16639,7 +16639,7 @@
         <v>280</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D192" s="1" t="s">
         <v>21</v>
@@ -16682,7 +16682,7 @@
         <v>225</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>234</v>
@@ -16842,7 +16842,7 @@
         <v>125</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>50</v>
@@ -16955,7 +16955,7 @@
         <v>397</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>68</v>
@@ -17377,7 +17377,7 @@
         <v>246</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D245" s="1" t="s">
         <v>21</v>
@@ -17406,7 +17406,7 @@
         <v>205</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>21</v>
@@ -17435,7 +17435,7 @@
         <v>513</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D249" s="1" t="s">
         <v>21</v>
@@ -17576,7 +17576,7 @@
         <v>250</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D259" s="1" t="s">
         <v>21</v>
@@ -17591,7 +17591,7 @@
         <v>342</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D260" s="1" t="s">
         <v>21</v>
@@ -17638,7 +17638,7 @@
         <v>100</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D264" s="1" t="s">
         <v>21</v>
@@ -17736,7 +17736,7 @@
         <v>145</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D271" s="1" t="s">
         <v>50</v>
@@ -17765,7 +17765,7 @@
         <v>1016</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D273" s="1" t="s">
         <v>21</v>
@@ -17891,7 +17891,7 @@
         <v>141</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D282" s="1" t="s">
         <v>23</v>
@@ -17905,7 +17905,7 @@
         <v>571</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D283" s="1" t="s">
         <v>21</v>
@@ -18061,7 +18061,7 @@
         <v>1166</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>21</v>
@@ -18299,7 +18299,7 @@
         <v>160</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D311" s="1" t="s">
         <v>307</v>
@@ -18346,7 +18346,7 @@
         <v>656</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D315" s="1" t="s">
         <v>21</v>
@@ -18402,7 +18402,7 @@
         <v>200</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>569</v>
+        <v>656</v>
       </c>
       <c r="D319" s="1" t="s">
         <v>21</v>
@@ -18603,7 +18603,7 @@
         <v>40</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D334" s="1" t="s">
         <v>50</v>
@@ -18617,7 +18617,7 @@
         <v>175</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D335" s="1" t="s">
         <v>21</v>
@@ -18659,7 +18659,7 @@
         <v>39</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D338" s="1" t="s">
         <v>50</v>
@@ -18674,7 +18674,7 @@
         <v>475</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D339" s="1" t="s">
         <v>21</v>
@@ -18731,7 +18731,7 @@
         <v>208</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D343" s="1" t="s">
         <v>21</v>
@@ -18871,7 +18871,7 @@
         <v>140</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D353" s="1" t="s">
         <v>50</v>
@@ -18899,7 +18899,7 @@
         <v>1500</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D355" s="1" t="s">
         <v>21</v>
@@ -18913,7 +18913,7 @@
         <v>325</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D356" s="1" t="s">
         <v>21</v>
@@ -19081,7 +19081,7 @@
         <v>60</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D368" s="1" t="s">
         <v>21</v>
@@ -19109,7 +19109,7 @@
         <v>5000</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D370" s="1" t="s">
         <v>21</v>
@@ -19165,7 +19165,7 @@
         <v>150</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D374" s="1" t="s">
         <v>21</v>
@@ -19180,7 +19180,7 @@
         <v>296</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D375" s="1" t="s">
         <v>21</v>
@@ -19194,7 +19194,7 @@
         <v>80</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D376" s="1" t="s">
         <v>23</v>
@@ -19396,7 +19396,7 @@
         <v>1414</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D391" s="1" t="s">
         <v>21</v>
@@ -19438,7 +19438,7 @@
         <v>40</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D394" s="1" t="s">
         <v>50</v>
@@ -19541,7 +19541,7 @@
         <v>572</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D402" s="1" t="s">
         <v>21</v>
@@ -19555,7 +19555,7 @@
         <v>161</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D403" s="1" t="s">
         <v>21</v>
@@ -19569,7 +19569,7 @@
         <v>100</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D404" s="1" t="s">
         <v>400</v>
@@ -19822,7 +19822,7 @@
         <v>235</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D422" s="1" t="s">
         <v>21</v>
@@ -19934,7 +19934,7 @@
         <v>160</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D430" s="1" t="s">
         <v>21</v>
@@ -19949,7 +19949,7 @@
         <v>300</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D431" s="1" t="s">
         <v>400</v>
@@ -20020,7 +20020,7 @@
         <v>154</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D436" s="1" t="s">
         <v>21</v>
@@ -20048,7 +20048,7 @@
         <v>75</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D438" s="1" t="s">
         <v>21</v>
@@ -20063,7 +20063,7 @@
         <v>750</v>
       </c>
       <c r="C439" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D439" s="1" t="s">
         <v>21</v>
@@ -20148,7 +20148,7 @@
         <v>658</v>
       </c>
       <c r="C445" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D445" s="1" t="s">
         <v>21</v>
@@ -20191,7 +20191,7 @@
         <v>890</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D448" s="1" t="s">
         <v>23</v>
@@ -20220,7 +20220,7 @@
         <v>373</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D450" s="1" t="s">
         <v>21</v>
@@ -20450,7 +20450,7 @@
         <v>125</v>
       </c>
       <c r="C467" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D467" s="1" t="s">
         <v>21</v>
@@ -20464,7 +20464,7 @@
         <v>500</v>
       </c>
       <c r="C468" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D468" s="1" t="s">
         <v>40</v>
@@ -20931,7 +20931,7 @@
         <v>150</v>
       </c>
       <c r="C502" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D502" s="1" t="s">
         <v>408</v>
@@ -20959,7 +20959,7 @@
         <v>100</v>
       </c>
       <c r="C504" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D504" s="1" t="s">
         <v>23</v>
@@ -21001,7 +21001,7 @@
         <v>110</v>
       </c>
       <c r="C507" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D507" s="1" t="s">
         <v>408</v>
@@ -21072,7 +21072,7 @@
         <v>530</v>
       </c>
       <c r="C512" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D512" s="1" t="s">
         <v>21</v>
@@ -21171,7 +21171,7 @@
         <v>285</v>
       </c>
       <c r="C519" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D519" s="1" t="s">
         <v>21</v>
@@ -21186,7 +21186,7 @@
         <v>540</v>
       </c>
       <c r="C520" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D520" s="1" t="s">
         <v>21</v>
@@ -21228,7 +21228,7 @@
         <v>195</v>
       </c>
       <c r="C523" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D523" s="1" t="s">
         <v>408</v>
@@ -21242,7 +21242,7 @@
         <v>105</v>
       </c>
       <c r="C524" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D524" s="1" t="s">
         <v>21</v>
@@ -21270,7 +21270,7 @@
         <v>60</v>
       </c>
       <c r="C526" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D526" s="1" t="s">
         <v>415</v>
@@ -21285,7 +21285,7 @@
         <v>185</v>
       </c>
       <c r="C527" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D527" s="1" t="s">
         <v>408</v>
@@ -21327,7 +21327,7 @@
         <v>275</v>
       </c>
       <c r="C530" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D530" s="1" t="s">
         <v>21</v>
@@ -21355,7 +21355,7 @@
         <v>160</v>
       </c>
       <c r="C532" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D532" s="1" t="s">
         <v>21</v>
@@ -21389,7 +21389,7 @@
         <v>868</v>
       </c>
       <c r="C535" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D535" s="1" t="s">
         <v>21</v>
@@ -21403,7 +21403,7 @@
         <v>80</v>
       </c>
       <c r="C536" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D536" s="1" t="s">
         <v>21</v>
@@ -21431,7 +21431,7 @@
         <v>55</v>
       </c>
       <c r="C538" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D538" s="1" t="s">
         <v>23</v>
@@ -21459,7 +21459,7 @@
         <v>60</v>
       </c>
       <c r="C540" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D540" s="1" t="s">
         <v>36</v>
@@ -21487,7 +21487,7 @@
         <v>60</v>
       </c>
       <c r="C542" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D542" s="1" t="s">
         <v>408</v>
@@ -21543,7 +21543,7 @@
         <v>60</v>
       </c>
       <c r="C546" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D546" s="1" t="s">
         <v>21</v>
@@ -21656,7 +21656,7 @@
         <v>155</v>
       </c>
       <c r="C554" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D554" s="1" t="s">
         <v>21</v>
@@ -21712,7 +21712,7 @@
         <v>80</v>
       </c>
       <c r="C558" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D558" s="1" t="s">
         <v>21</v>
@@ -21811,7 +21811,7 @@
         <v>345</v>
       </c>
       <c r="C565" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D565" s="1" t="s">
         <v>36</v>
@@ -21895,7 +21895,7 @@
         <v>105</v>
       </c>
       <c r="C571" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D571" s="1" t="s">
         <v>36</v>
@@ -22078,7 +22078,7 @@
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A586" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B586" s="1">
         <v>16153</v>
@@ -22086,7 +22086,7 @@
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A587" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B587" s="1">
         <f>B584-B585-B586</f>
